--- a/FY28/RSU5_FY28_Projection.xlsx
+++ b/FY28/RSU5_FY28_Projection.xlsx
@@ -37,6 +37,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-LegalAnalysis" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-DOEStaffing" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-PathC" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-PathD" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-Capacity" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-FacilitiesRisk" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-RSUImpact" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-StateBenchmarks" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-EducationQuality" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,16 +52,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="+#,##0;-#,##0;0"/>
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="169" formatCode="+0.000;-0.000;0.000"/>
     <numFmt numFmtId="170" formatCode="+0.0%;-0.0%;0.0%"/>
+    <numFmt numFmtId="171" formatCode="+#,##0;-#,##0"/>
+    <numFmt numFmtId="172" formatCode="$#,##0"/>
+    <numFmt numFmtId="173" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +102,12 @@
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -178,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,9 +210,9 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,21 +225,21 @@
     <xf numFmtId="10" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,15 +250,15 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,6 +280,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -869,7 +913,7 @@
           <t>Additional bus routes (Pownal -&gt; DCS)</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B30" s="73" t="n">
         <v>-225000</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -884,7 +928,7 @@
           <t>PES building conversion (PreK center)</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="73" t="n">
         <v>-74375</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -899,7 +943,7 @@
           <t>DCS capacity/coordination costs</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B32" s="73" t="n">
         <v>-75000</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -914,7 +958,7 @@
           <t>EC program opt-out risk (families choosing private)</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="73" t="n">
         <v>-50000</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -929,7 +973,7 @@
           <t>PATH B NET ANNUAL RESULT</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="74">
         <f>B29+B30+B31+B32+B33</f>
         <v/>
       </c>
@@ -971,11 +1015,11 @@
           <t>Annual budget impact</t>
         </is>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="75">
         <f>B22</f>
         <v/>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="75">
         <f>B34</f>
         <v/>
       </c>
@@ -1545,7 +1589,7 @@
           <t>Total reductions applied</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="81" t="n">
         <v>-1715649</v>
       </c>
     </row>
@@ -1555,7 +1599,7 @@
           <t>Redirected to reserves</t>
         </is>
       </c>
-      <c r="B19" s="33" t="n">
+      <c r="B19" s="81" t="n">
         <v>-75000</v>
       </c>
     </row>
@@ -1627,10 +1671,10 @@
       <c r="D24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="E24" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1653,10 +1697,10 @@
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="33" t="n">
+      <c r="E25" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1679,10 +1723,10 @@
       <c r="D26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1705,10 +1749,10 @@
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="81" t="n">
         <v>-26925</v>
       </c>
-      <c r="F27" s="33" t="n">
+      <c r="F27" s="81" t="n">
         <v>-26925</v>
       </c>
     </row>
@@ -1731,10 +1775,10 @@
       <c r="D28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="81" t="n">
         <v>-26756</v>
       </c>
-      <c r="F28" s="33" t="n">
+      <c r="F28" s="81" t="n">
         <v>-26756</v>
       </c>
     </row>
@@ -1757,10 +1801,10 @@
       <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="33" t="n">
+      <c r="E29" s="81" t="n">
         <v>-53850</v>
       </c>
-      <c r="F29" s="33" t="n">
+      <c r="F29" s="81" t="n">
         <v>-53850</v>
       </c>
     </row>
@@ -1783,10 +1827,10 @@
       <c r="D30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="81" t="n">
         <v>-26925</v>
       </c>
-      <c r="F30" s="33" t="n">
+      <c r="F30" s="81" t="n">
         <v>-26925</v>
       </c>
     </row>
@@ -1809,10 +1853,10 @@
       <c r="D31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="33" t="n">
+      <c r="E31" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F31" s="33" t="n">
+      <c r="F31" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1835,10 +1879,10 @@
       <c r="D32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F32" s="33" t="n">
+      <c r="F32" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1861,10 +1905,10 @@
       <c r="D33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="33" t="n">
+      <c r="E33" s="81" t="n">
         <v>-21738</v>
       </c>
-      <c r="F33" s="33" t="n">
+      <c r="F33" s="81" t="n">
         <v>-21738</v>
       </c>
     </row>
@@ -1887,10 +1931,10 @@
       <c r="D34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F34" s="33" t="n">
+      <c r="F34" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -1913,10 +1957,10 @@
       <c r="D35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="33" t="n">
+      <c r="E35" s="81" t="n">
         <v>-57059</v>
       </c>
-      <c r="F35" s="33" t="n">
+      <c r="F35" s="81" t="n">
         <v>-57059</v>
       </c>
     </row>
@@ -1939,10 +1983,10 @@
       <c r="D36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="33" t="n">
+      <c r="E36" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F36" s="33" t="n">
+      <c r="F36" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -2004,10 +2048,10 @@
       <c r="D40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="33" t="n">
+      <c r="E40" s="81" t="n">
         <v>-52600</v>
       </c>
-      <c r="F40" s="33" t="n">
+      <c r="F40" s="81" t="n">
         <v>-52600</v>
       </c>
     </row>
@@ -2030,10 +2074,10 @@
       <c r="D41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="33" t="n">
+      <c r="E41" s="81" t="n">
         <v>-52600</v>
       </c>
-      <c r="F41" s="33" t="n">
+      <c r="F41" s="81" t="n">
         <v>-52600</v>
       </c>
     </row>
@@ -2056,10 +2100,10 @@
       <c r="D42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="33" t="n">
+      <c r="E42" s="81" t="n">
         <v>-52600</v>
       </c>
-      <c r="F42" s="33" t="n">
+      <c r="F42" s="81" t="n">
         <v>-52600</v>
       </c>
     </row>
@@ -2082,10 +2126,10 @@
       <c r="D43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="33" t="n">
+      <c r="E43" s="81" t="n">
         <v>-52600</v>
       </c>
-      <c r="F43" s="33" t="n">
+      <c r="F43" s="81" t="n">
         <v>-52600</v>
       </c>
     </row>
@@ -2108,10 +2152,10 @@
       <c r="D44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="33" t="n">
+      <c r="E44" s="81" t="n">
         <v>-52600</v>
       </c>
-      <c r="F44" s="33" t="n">
+      <c r="F44" s="81" t="n">
         <v>-52600</v>
       </c>
     </row>
@@ -2134,10 +2178,10 @@
       <c r="D45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="33" t="n">
+      <c r="E45" s="81" t="n">
         <v>-107700</v>
       </c>
-      <c r="F45" s="33" t="n">
+      <c r="F45" s="81" t="n">
         <v>-107700</v>
       </c>
     </row>
@@ -2160,10 +2204,10 @@
       <c r="D46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="33" t="n">
+      <c r="E46" s="81" t="n">
         <v>-69796</v>
       </c>
-      <c r="F46" s="33" t="n">
+      <c r="F46" s="81" t="n">
         <v>-69796</v>
       </c>
     </row>
@@ -2225,10 +2269,10 @@
       <c r="D50" s="5" t="n">
         <v>336758</v>
       </c>
-      <c r="E50" s="33" t="n">
+      <c r="E50" s="81" t="n">
         <v>-250000</v>
       </c>
-      <c r="F50" s="33" t="n">
+      <c r="F50" s="81" t="n">
         <v>86758</v>
       </c>
     </row>
@@ -2251,10 +2295,10 @@
       <c r="D51" s="5" t="n">
         <v>116000</v>
       </c>
-      <c r="E51" s="33" t="n">
+      <c r="E51" s="81" t="n">
         <v>-58000</v>
       </c>
-      <c r="F51" s="33" t="n">
+      <c r="F51" s="81" t="n">
         <v>58000</v>
       </c>
     </row>
@@ -2277,10 +2321,10 @@
       <c r="D52" s="5" t="n">
         <v>75000</v>
       </c>
-      <c r="E52" s="33" t="n">
+      <c r="E52" s="81" t="n">
         <v>-75000</v>
       </c>
-      <c r="F52" s="33" t="n">
+      <c r="F52" s="81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2794,7 +2838,7 @@
       <c r="B19" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="78" t="n">
         <v>2.5</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2812,7 +2856,7 @@
       <c r="B20" s="5" t="n">
         <v>278</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="78" t="n">
         <v>16</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2830,7 +2874,7 @@
       <c r="B21" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="78" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2848,7 +2892,7 @@
       <c r="B22" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="78" t="n">
         <v>6</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2863,7 +2907,7 @@
           <t>DCS Check Total</t>
         </is>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="82">
         <f>C19+C20+C21+C22</f>
         <v/>
       </c>
@@ -3008,10 +3052,10 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B35" s="28" t="n">
+      <c r="B35" s="78" t="n">
         <v>6.5</v>
       </c>
-      <c r="C35" s="28" t="n">
+      <c r="C35" s="78" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="37">
@@ -3030,10 +3074,10 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B36" s="28" t="n">
+      <c r="B36" s="78" t="n">
         <v>26.5</v>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C36" s="78" t="n">
         <v>23</v>
       </c>
       <c r="D36" s="37">
@@ -3052,10 +3096,10 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n">
+      <c r="B37" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="78" t="n">
         <v>16</v>
       </c>
       <c r="D37" s="37">
@@ -3074,10 +3118,10 @@
           <t>MLS</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n">
+      <c r="B38" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C38" s="78" t="n">
         <v>15</v>
       </c>
       <c r="D38" s="37">
@@ -3096,10 +3140,10 @@
           <t>FMS</t>
         </is>
       </c>
-      <c r="B39" s="28" t="n">
+      <c r="B39" s="78" t="n">
         <v>15.5</v>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C39" s="78" t="n">
         <v>13</v>
       </c>
       <c r="D39" s="37">
@@ -3118,11 +3162,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="38">
+      <c r="B41" s="83">
         <f>SUM(B35:B39)</f>
         <v/>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="83">
         <f>SUM(C35:C39)</f>
         <v/>
       </c>
@@ -3137,7 +3181,7 @@
           <t>Net FTE Saved (Scenario 2)</t>
         </is>
       </c>
-      <c r="B42" s="40">
+      <c r="B42" s="84">
         <f>-D41</f>
         <v/>
       </c>
@@ -3294,37 +3338,37 @@
           <t>PES (Pownal Elementary)</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="78" t="n">
         <v>26.3</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="78" t="n">
         <v>33.8</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="78" t="n">
         <v>29.6</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="78" t="n">
         <v>28</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="78" t="n">
         <v>27.7</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="78" t="n">
         <v>27.3</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="78" t="n">
         <v>24.5</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="78" t="n">
         <v>22.5</v>
       </c>
-      <c r="J11" s="28" t="n">
+      <c r="J11" s="78" t="n">
         <v>22.9</v>
       </c>
-      <c r="K11" s="28" t="n">
+      <c r="K11" s="78" t="n">
         <v>21.5</v>
       </c>
-      <c r="L11" s="28" t="n">
+      <c r="L11" s="78" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -3334,37 +3378,37 @@
           <t>DCS (Durham Community)</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="78" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="78" t="n">
         <v>88</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="78" t="n">
         <v>84.8</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="78" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="78" t="n">
         <v>94.2</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="78" t="n">
         <v>93</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="78" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="78" t="n">
         <v>83.5</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="78" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="78" t="n">
         <v>88.8</v>
       </c>
-      <c r="L12" s="28" t="n">
+      <c r="L12" s="78" t="n">
         <v>85.7</v>
       </c>
     </row>
@@ -3374,37 +3418,37 @@
           <t>MSS (Morse Street)</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="78" t="n">
         <v>42.1</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="78" t="n">
         <v>42.7</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="78" t="n">
         <v>50.5</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="78" t="n">
         <v>57.1</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="78" t="n">
         <v>55.7</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="78" t="n">
         <v>55.5</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="78" t="n">
         <v>60.8</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="78" t="n">
         <v>58.5</v>
       </c>
-      <c r="J13" s="28" t="n">
+      <c r="J13" s="78" t="n">
         <v>59.8</v>
       </c>
-      <c r="K13" s="28" t="n">
+      <c r="K13" s="78" t="n">
         <v>64.7</v>
       </c>
-      <c r="L13" s="28" t="n">
+      <c r="L13" s="78" t="n">
         <v>55</v>
       </c>
     </row>
@@ -3414,37 +3458,37 @@
           <t>MLS (Mast Landing)</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="78" t="n">
         <v>37</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="78" t="n">
         <v>48.2</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="78" t="n">
         <v>46.4</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="78" t="n">
         <v>50.2</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="78" t="n">
         <v>55.2</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="78" t="n">
         <v>46.4</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="78" t="n">
         <v>50.5</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="78" t="n">
         <v>49.1</v>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="78" t="n">
         <v>45.7</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="78" t="n">
         <v>53.8</v>
       </c>
-      <c r="L14" s="28" t="n">
+      <c r="L14" s="78" t="n">
         <v>50.5</v>
       </c>
     </row>
@@ -3454,37 +3498,37 @@
           <t>FMS (Freeport Middle)</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="78" t="n">
         <v>63.9</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="78" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="78" t="n">
         <v>75.7</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="78" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="78" t="n">
         <v>71.7</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="78" t="n">
         <v>58.9</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="78" t="n">
         <v>67.8</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="78" t="n">
         <v>69.7</v>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="78" t="n">
         <v>62.8</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="78" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L15" s="28" t="n">
+      <c r="L15" s="78" t="n">
         <v>66.40000000000001</v>
       </c>
     </row>
@@ -3494,37 +3538,37 @@
           <t>FHS (Freeport High)</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="78" t="n">
         <v>102</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="78" t="n">
         <v>112.5</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="78" t="n">
         <v>106</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="78" t="n">
         <v>124.1</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="78" t="n">
         <v>123.1</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="78" t="n">
         <v>112.4</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="78" t="n">
         <v>100.4</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="78" t="n">
         <v>100</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="78" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="78" t="n">
         <v>108</v>
       </c>
-      <c r="L16" s="28" t="n">
+      <c r="L16" s="78" t="n">
         <v>98.5</v>
       </c>
     </row>
@@ -3534,37 +3578,37 @@
           <t>District-wide</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="78" t="n">
         <v>103.9</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="78" t="n">
         <v>123.4</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="78" t="n">
         <v>111.4</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="78" t="n">
         <v>125.4</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="78" t="n">
         <v>115.4</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="78" t="n">
         <v>118.9</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="78" t="n">
         <v>119.8</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="78" t="n">
         <v>129.9</v>
       </c>
-      <c r="J17" s="28" t="n">
+      <c r="J17" s="78" t="n">
         <v>116.2</v>
       </c>
-      <c r="K17" s="28" t="n">
+      <c r="K17" s="78" t="n">
         <v>144.3</v>
       </c>
-      <c r="L17" s="28" t="n">
+      <c r="L17" s="78" t="n">
         <v>139.8</v>
       </c>
     </row>
@@ -3574,47 +3618,47 @@
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="82">
         <f>SUM(B11:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="82">
         <f>SUM(C11:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="82">
         <f>SUM(D11:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="82">
         <f>SUM(E11:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="82">
         <f>SUM(F11:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="82">
         <f>SUM(G11:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="82">
         <f>SUM(H11:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="82">
         <f>SUM(I11:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="82">
         <f>SUM(J11:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="82">
         <f>SUM(K11:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="82">
         <f>SUM(L11:L17)</f>
         <v/>
       </c>
@@ -3701,37 +3745,37 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="78" t="n">
         <v>10.4</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="78" t="n">
         <v>10.2</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="78" t="n">
         <v>6.3</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="78" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="78" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="G23" s="78" t="n">
         <v>10.2</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="78" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="78" t="n">
         <v>10.8</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="J23" s="78" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K23" s="28" t="n">
+      <c r="K23" s="78" t="n">
         <v>10.2</v>
       </c>
-      <c r="L23" s="28" t="n">
+      <c r="L23" s="78" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -3741,37 +3785,37 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="78" t="n">
         <v>26</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="78" t="n">
         <v>31.3</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="78" t="n">
         <v>25.5</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="78" t="n">
         <v>30</v>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F24" s="78" t="n">
         <v>31</v>
       </c>
-      <c r="G24" s="28" t="n">
+      <c r="G24" s="78" t="n">
         <v>34</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="78" t="n">
         <v>33</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="78" t="n">
         <v>33.5</v>
       </c>
-      <c r="J24" s="28" t="n">
+      <c r="J24" s="78" t="n">
         <v>34.5</v>
       </c>
-      <c r="K24" s="28" t="n">
+      <c r="K24" s="78" t="n">
         <v>34.5</v>
       </c>
-      <c r="L24" s="28" t="n">
+      <c r="L24" s="78" t="n">
         <v>35.5</v>
       </c>
     </row>
@@ -3781,37 +3825,37 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="78" t="n">
         <v>16</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="78" t="n">
         <v>16.2</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="78" t="n">
         <v>16.3</v>
       </c>
-      <c r="E25" s="28" t="n">
+      <c r="E25" s="78" t="n">
         <v>18.5</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="78" t="n">
         <v>19.8</v>
       </c>
-      <c r="G25" s="28" t="n">
+      <c r="G25" s="78" t="n">
         <v>20.8</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="78" t="n">
         <v>21.2</v>
       </c>
-      <c r="I25" s="28" t="n">
+      <c r="I25" s="78" t="n">
         <v>20.6</v>
       </c>
-      <c r="J25" s="28" t="n">
+      <c r="J25" s="78" t="n">
         <v>21.6</v>
       </c>
-      <c r="K25" s="28" t="n">
+      <c r="K25" s="78" t="n">
         <v>21.2</v>
       </c>
-      <c r="L25" s="28" t="n">
+      <c r="L25" s="78" t="n">
         <v>19.2</v>
       </c>
     </row>
@@ -3821,37 +3865,37 @@
           <t>MLS</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="78" t="n">
         <v>14.6</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="78" t="n">
         <v>17.6</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="78" t="n">
         <v>16.5</v>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E26" s="78" t="n">
         <v>17.7</v>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="F26" s="78" t="n">
         <v>16.7</v>
       </c>
-      <c r="G26" s="28" t="n">
+      <c r="G26" s="78" t="n">
         <v>17.6</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="78" t="n">
         <v>16.6</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="I26" s="78" t="n">
         <v>17.6</v>
       </c>
-      <c r="J26" s="28" t="n">
+      <c r="J26" s="78" t="n">
         <v>16.6</v>
       </c>
-      <c r="K26" s="28" t="n">
+      <c r="K26" s="78" t="n">
         <v>19.6</v>
       </c>
-      <c r="L26" s="28" t="n">
+      <c r="L26" s="78" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -3861,37 +3905,37 @@
           <t>FMS</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="78" t="n">
         <v>25.5</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="78" t="n">
         <v>26.2</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="78" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="78" t="n">
         <v>24.5</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="78" t="n">
         <v>23.9</v>
       </c>
-      <c r="G27" s="28" t="n">
+      <c r="G27" s="78" t="n">
         <v>22.1</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="78" t="n">
         <v>23.5</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I27" s="78" t="n">
         <v>23.5</v>
       </c>
-      <c r="J27" s="28" t="n">
+      <c r="J27" s="78" t="n">
         <v>24</v>
       </c>
-      <c r="K27" s="28" t="n">
+      <c r="K27" s="78" t="n">
         <v>23.5</v>
       </c>
-      <c r="L27" s="28" t="n">
+      <c r="L27" s="78" t="n">
         <v>23.3</v>
       </c>
     </row>
@@ -3901,37 +3945,37 @@
           <t>FHS</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="78" t="n">
         <v>37</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="78" t="n">
         <v>39.1</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="78" t="n">
         <v>34.5</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E28" s="78" t="n">
         <v>38.6</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="78" t="n">
         <v>40.7</v>
       </c>
-      <c r="G28" s="28" t="n">
+      <c r="G28" s="78" t="n">
         <v>42.2</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="78" t="n">
         <v>42.2</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="78" t="n">
         <v>42.7</v>
       </c>
-      <c r="J28" s="28" t="n">
+      <c r="J28" s="78" t="n">
         <v>42.7</v>
       </c>
-      <c r="K28" s="28" t="n">
+      <c r="K28" s="78" t="n">
         <v>42.6</v>
       </c>
-      <c r="L28" s="28" t="n">
+      <c r="L28" s="78" t="n">
         <v>41.7</v>
       </c>
     </row>
@@ -4017,37 +4061,37 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="78" t="n">
         <v>1.8</v>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C33" s="78" t="n">
         <v>1.8</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E33" s="78" t="n">
         <v>0.5</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="28" t="n">
+      <c r="G33" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="28" t="n">
+      <c r="I33" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="28" t="n">
+      <c r="J33" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="28" t="n">
+      <c r="K33" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="28" t="n">
+      <c r="L33" s="78" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4057,37 +4101,37 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n">
+      <c r="B34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C34" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E34" s="78" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="28" t="n">
+      <c r="G34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="28" t="n">
+      <c r="J34" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="28" t="n">
+      <c r="K34" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="L34" s="28" t="n">
+      <c r="L34" s="78" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -4097,37 +4141,37 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="B35" s="28" t="n">
+      <c r="B35" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="28" t="n">
+      <c r="C35" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="28" t="n">
+      <c r="D35" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="28" t="n">
+      <c r="E35" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="28" t="n">
+      <c r="F35" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="28" t="n">
+      <c r="G35" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="28" t="n">
+      <c r="I35" s="78" t="n">
         <v>4.1</v>
       </c>
-      <c r="J35" s="28" t="n">
+      <c r="J35" s="78" t="n">
         <v>4.1</v>
       </c>
-      <c r="K35" s="28" t="n">
+      <c r="K35" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="L35" s="28" t="n">
+      <c r="L35" s="78" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -4137,37 +4181,37 @@
           <t>MLS</t>
         </is>
       </c>
-      <c r="B36" s="28" t="n">
+      <c r="B36" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C36" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="28" t="n">
+      <c r="D36" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="28" t="n">
+      <c r="E36" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="28" t="n">
+      <c r="G36" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="28" t="n">
+      <c r="I36" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="28" t="n">
+      <c r="J36" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="28" t="n">
+      <c r="K36" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="28" t="n">
+      <c r="L36" s="78" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -4177,37 +4221,37 @@
           <t>FMS</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n">
+      <c r="B37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="28" t="n">
+      <c r="D37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="28" t="n">
+      <c r="E37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="28" t="n">
+      <c r="F37" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="28" t="n">
+      <c r="G37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="H37" s="28" t="n">
+      <c r="H37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="28" t="n">
+      <c r="I37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="28" t="n">
+      <c r="J37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="28" t="n">
+      <c r="K37" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="L37" s="28" t="n">
+      <c r="L37" s="78" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -4217,37 +4261,37 @@
           <t>FHS</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n">
+      <c r="B38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C38" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="28" t="n">
+      <c r="D38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="28" t="n">
+      <c r="E38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="G38" s="28" t="n">
+      <c r="G38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="H38" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="28" t="n">
+      <c r="I38" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="J38" s="28" t="n">
+      <c r="J38" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="28" t="n">
+      <c r="K38" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="L38" s="28" t="n">
+      <c r="L38" s="78" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -4333,37 +4377,37 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B43" s="28" t="n">
+      <c r="B43" s="78" t="n">
         <v>6.4</v>
       </c>
-      <c r="C43" s="28" t="n">
+      <c r="C43" s="78" t="n">
         <v>7.4</v>
       </c>
-      <c r="D43" s="28" t="n">
+      <c r="D43" s="78" t="n">
         <v>5.7</v>
       </c>
-      <c r="E43" s="28" t="n">
+      <c r="E43" s="78" t="n">
         <v>4.7</v>
       </c>
-      <c r="F43" s="28" t="n">
+      <c r="F43" s="78" t="n">
         <v>4.2</v>
       </c>
-      <c r="G43" s="28" t="n">
+      <c r="G43" s="78" t="n">
         <v>4.5</v>
       </c>
-      <c r="H43" s="28" t="n">
+      <c r="H43" s="78" t="n">
         <v>3.1</v>
       </c>
-      <c r="I43" s="28" t="n">
+      <c r="I43" s="78" t="n">
         <v>2.1</v>
       </c>
-      <c r="J43" s="28" t="n">
+      <c r="J43" s="78" t="n">
         <v>5.1</v>
       </c>
-      <c r="K43" s="28" t="n">
+      <c r="K43" s="78" t="n">
         <v>3.1</v>
       </c>
-      <c r="L43" s="28" t="n">
+      <c r="L43" s="78" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4373,37 +4417,37 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B44" s="28" t="n">
+      <c r="B44" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="C44" s="28" t="n">
+      <c r="C44" s="78" t="n">
         <v>11</v>
       </c>
-      <c r="D44" s="28" t="n">
+      <c r="D44" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="E44" s="78" t="n">
         <v>13</v>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="G44" s="28" t="n">
+      <c r="G44" s="78" t="n">
         <v>14.5</v>
       </c>
-      <c r="H44" s="28" t="n">
+      <c r="H44" s="78" t="n">
         <v>16</v>
       </c>
-      <c r="I44" s="28" t="n">
+      <c r="I44" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="J44" s="28" t="n">
+      <c r="J44" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="K44" s="28" t="n">
+      <c r="K44" s="78" t="n">
         <v>13</v>
       </c>
-      <c r="L44" s="28" t="n">
+      <c r="L44" s="78" t="n">
         <v>13.5</v>
       </c>
     </row>
@@ -4413,37 +4457,37 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="B45" s="28" t="n">
+      <c r="B45" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="D45" s="28" t="n">
+      <c r="D45" s="78" t="n">
         <v>13.4</v>
       </c>
-      <c r="E45" s="28" t="n">
+      <c r="E45" s="78" t="n">
         <v>12.4</v>
       </c>
-      <c r="F45" s="28" t="n">
+      <c r="F45" s="78" t="n">
         <v>12.5</v>
       </c>
-      <c r="G45" s="28" t="n">
+      <c r="G45" s="78" t="n">
         <v>14</v>
       </c>
-      <c r="H45" s="28" t="n">
+      <c r="H45" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="I45" s="28" t="n">
+      <c r="I45" s="78" t="n">
         <v>14.6</v>
       </c>
-      <c r="J45" s="28" t="n">
+      <c r="J45" s="78" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="28" t="n">
+      <c r="K45" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="L45" s="28" t="n">
+      <c r="L45" s="78" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4453,37 +4497,37 @@
           <t>MLS</t>
         </is>
       </c>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="78" t="n">
         <v>6.1</v>
       </c>
-      <c r="C46" s="28" t="n">
+      <c r="C46" s="78" t="n">
         <v>5.6</v>
       </c>
-      <c r="D46" s="28" t="n">
+      <c r="D46" s="78" t="n">
         <v>4.5</v>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="E46" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F46" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="G46" s="28" t="n">
+      <c r="G46" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="H46" s="28" t="n">
+      <c r="H46" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="I46" s="28" t="n">
+      <c r="I46" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="J46" s="28" t="n">
+      <c r="J46" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="K46" s="28" t="n">
+      <c r="K46" s="78" t="n">
         <v>11</v>
       </c>
-      <c r="L46" s="28" t="n">
+      <c r="L46" s="78" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4493,37 +4537,37 @@
           <t>FMS</t>
         </is>
       </c>
-      <c r="B47" s="28" t="n">
+      <c r="B47" s="78" t="n">
         <v>8.5</v>
       </c>
-      <c r="C47" s="28" t="n">
+      <c r="C47" s="78" t="n">
         <v>10.5</v>
       </c>
-      <c r="D47" s="28" t="n">
+      <c r="D47" s="78" t="n">
         <v>13.5</v>
       </c>
-      <c r="E47" s="28" t="n">
+      <c r="E47" s="78" t="n">
         <v>12.5</v>
       </c>
-      <c r="F47" s="28" t="n">
+      <c r="F47" s="78" t="n">
         <v>11.5</v>
       </c>
-      <c r="G47" s="28" t="n">
+      <c r="G47" s="78" t="n">
         <v>9.1</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H47" s="78" t="n">
         <v>11.2</v>
       </c>
-      <c r="I47" s="28" t="n">
+      <c r="I47" s="78" t="n">
         <v>16.2</v>
       </c>
-      <c r="J47" s="28" t="n">
+      <c r="J47" s="78" t="n">
         <v>14.2</v>
       </c>
-      <c r="K47" s="28" t="n">
+      <c r="K47" s="78" t="n">
         <v>10.2</v>
       </c>
-      <c r="L47" s="28" t="n">
+      <c r="L47" s="78" t="n">
         <v>11.1</v>
       </c>
     </row>
@@ -4533,37 +4577,37 @@
           <t>FHS</t>
         </is>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="C48" s="28" t="n">
+      <c r="C48" s="78" t="n">
         <v>11.3</v>
       </c>
-      <c r="D48" s="28" t="n">
+      <c r="D48" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="E48" s="28" t="n">
+      <c r="E48" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F48" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="G48" s="28" t="n">
+      <c r="G48" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="H48" s="28" t="n">
+      <c r="H48" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="I48" s="28" t="n">
+      <c r="I48" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="J48" s="28" t="n">
+      <c r="J48" s="78" t="n">
         <v>5.5</v>
       </c>
-      <c r="K48" s="28" t="n">
+      <c r="K48" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="L48" s="28" t="n">
+      <c r="L48" s="78" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4735,7 +4779,7 @@
           <t>Pownal Share of RSU 5 Budget</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="80" t="n">
         <v>0.106</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5814,7 +5858,7 @@
           <t>Current total mil rate</t>
         </is>
       </c>
-      <c r="B113" s="30" t="n">
+      <c r="B113" s="79" t="n">
         <v>15.3</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -5829,7 +5873,7 @@
           <t>Current RSU share of mil rate</t>
         </is>
       </c>
-      <c r="B114" s="30" t="n">
+      <c r="B114" s="79" t="n">
         <v>8.935</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -6108,7 +6152,7 @@
           <t>Additional teaching FTE for grades 6-8</t>
         </is>
       </c>
-      <c r="B132" s="28" t="n">
+      <c r="B132" s="78" t="n">
         <v>5</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -6277,8 +6321,8 @@
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="A95:F95"/>
@@ -7511,13 +7555,13 @@
           <t>Total mil rate (FY26)</t>
         </is>
       </c>
-      <c r="B99" s="30" t="n">
+      <c r="B99" s="79" t="n">
         <v>15.3</v>
       </c>
-      <c r="C99" s="30" t="n">
+      <c r="C99" s="79" t="n">
         <v>33.58</v>
       </c>
-      <c r="D99" s="30" t="n">
+      <c r="D99" s="79" t="n">
         <v>13.85</v>
       </c>
     </row>
@@ -7527,13 +7571,13 @@
           <t>Assessment ratio</t>
         </is>
       </c>
-      <c r="B100" s="31" t="n">
+      <c r="B100" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="C100" s="31" t="n">
+      <c r="C100" s="80" t="n">
         <v>0.53</v>
       </c>
-      <c r="D100" s="31" t="n">
+      <c r="D100" s="80" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7559,7 +7603,7 @@
           <t>RSU share of tax bill (FY26)</t>
         </is>
       </c>
-      <c r="B102" s="31" t="n">
+      <c r="B102" s="80" t="n">
         <v>0.584</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -7567,7 +7611,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D102" s="31" t="n">
+      <c r="D102" s="80" t="n">
         <v>0.716</v>
       </c>
     </row>
@@ -7788,7 +7832,7 @@
           <t>PES avg K-5 grade size</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="82">
         <f>AVERAGE('I-Enrollment'!B21:'I-Enrollment'!B26)</f>
         <v/>
       </c>
@@ -7799,7 +7843,7 @@
           <t>DCS avg 7-8 grade size</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="82">
         <f>AVERAGE('I-Enrollment'!B32,'I-Enrollment'!B33)</f>
         <v/>
       </c>
@@ -8286,7 +8330,7 @@
         <f>'C-Budget'!D7</f>
         <v/>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="85">
         <f>1</f>
         <v/>
       </c>
@@ -8305,7 +8349,7 @@
         <f>'C-Budget'!F7</f>
         <v/>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="85">
         <f>'C-Enrollment'!B11/'I-Enrollment'!F14</f>
         <v/>
       </c>
@@ -8324,7 +8368,7 @@
         <f>'C-Budget'!G7</f>
         <v/>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="85">
         <f>'C-Enrollment'!B12/'I-Enrollment'!F15</f>
         <v/>
       </c>
@@ -8343,7 +8387,7 @@
         <f>'C-Budget'!B13</f>
         <v/>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="85">
         <f>'C-Enrollment'!E16/'C-Enrollment'!E19</f>
         <v/>
       </c>
@@ -8413,7 +8457,7 @@
         <f>'C-Budget'!B7</f>
         <v/>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="85">
         <f>1</f>
         <v/>
       </c>
@@ -8432,7 +8476,7 @@
         <f>'C-Budget'!G7</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="85">
         <f>'C-Enrollment'!C12/'I-Enrollment'!F15</f>
         <v/>
       </c>
@@ -8451,7 +8495,7 @@
         <f>'C-Budget'!B13</f>
         <v/>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="85">
         <f>'C-Enrollment'!E17/'C-Enrollment'!E19</f>
         <v/>
       </c>
@@ -8521,7 +8565,7 @@
         <f>'C-Budget'!C7</f>
         <v/>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="85">
         <f>1</f>
         <v/>
       </c>
@@ -8540,7 +8584,7 @@
         <f>'C-Budget'!E7</f>
         <v/>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="85">
         <f>1</f>
         <v/>
       </c>
@@ -8559,7 +8603,7 @@
         <f>'C-Budget'!F7</f>
         <v/>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="85">
         <f>'C-Enrollment'!D11/'I-Enrollment'!F14</f>
         <v/>
       </c>
@@ -8578,7 +8622,7 @@
         <f>'C-Budget'!G7</f>
         <v/>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="85">
         <f>'C-Enrollment'!D12/'I-Enrollment'!F15</f>
         <v/>
       </c>
@@ -8597,7 +8641,7 @@
         <f>'C-Budget'!B13</f>
         <v/>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="85">
         <f>'C-Enrollment'!E18/'C-Enrollment'!E19</f>
         <v/>
       </c>
@@ -8890,7 +8934,7 @@
         <f>'C-Consumption'!D11</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="76">
         <f>B18-C18</f>
         <v/>
       </c>
@@ -8921,7 +8965,7 @@
         <f>'C-Consumption'!D19</f>
         <v/>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="76">
         <f>B19-C19</f>
         <v/>
       </c>
@@ -8952,7 +8996,7 @@
         <f>'C-Consumption'!D29</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="76">
         <f>B20-C20</f>
         <v/>
       </c>
@@ -9457,7 +9501,7 @@
         <f>B12/'I-Tax'!B13*1000</f>
         <v/>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="85">
         <f>'I-Tax'!B13/'I-Tax'!B14</f>
         <v/>
       </c>
@@ -9484,7 +9528,7 @@
         <f>B13/'I-Tax'!B34*1000</f>
         <v/>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="85">
         <f>'I-Tax'!B34/'I-Tax'!B35</f>
         <v/>
       </c>
@@ -9511,7 +9555,7 @@
         <f>B14/'I-Tax'!B24*1000</f>
         <v/>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="85">
         <f>'I-Tax'!B24/'I-Tax'!B25</f>
         <v/>
       </c>
@@ -9703,7 +9747,7 @@
         <f>AVERAGE(C6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="73">
         <f>B6-F6</f>
         <v/>
       </c>
@@ -9734,7 +9778,7 @@
         <f>AVERAGE(C7:E7)</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="73">
         <f>B7-F7</f>
         <v/>
       </c>
@@ -9765,7 +9809,7 @@
         <f>AVERAGE(C8:E8)</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="73">
         <f>B8-F8</f>
         <v/>
       </c>
@@ -9796,7 +9840,7 @@
         <f>AVERAGE(C9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="73">
         <f>B9-F9</f>
         <v/>
       </c>
@@ -9827,7 +9871,7 @@
         <f>AVERAGE(C10:E10)</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="73">
         <f>B10-F10</f>
         <v/>
       </c>
@@ -9858,7 +9902,7 @@
         <f>AVERAGE(C11:E11)</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="73">
         <f>B11-F11</f>
         <v/>
       </c>
@@ -9877,7 +9921,7 @@
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="76">
         <f>B12-F12</f>
         <v/>
       </c>
@@ -9999,7 +10043,7 @@
           <t>Tier 1 reductions (staff positions)</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="73">
         <f>SUM('I-FY27Reductions'!F24:'I-FY27Reductions'!F36)</f>
         <v/>
       </c>
@@ -10010,7 +10054,7 @@
           <t>Tier 2 reductions (support positions)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="73">
         <f>SUM('I-FY27Reductions'!F40:'I-FY27Reductions'!F46)</f>
         <v/>
       </c>
@@ -10021,7 +10065,7 @@
           <t>Other reductions (tech, facilities)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="73">
         <f>SUM('I-FY27Reductions'!E50:'I-FY27Reductions'!E52)</f>
         <v/>
       </c>
@@ -10032,7 +10076,7 @@
           <t>TOTAL REDUCTIONS</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="76">
         <f>B13+B14+B15</f>
         <v/>
       </c>
@@ -10110,14 +10154,14 @@
           <t>Additional cuts beyond proposed</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="73">
         <f>B20-C20</f>
         <v/>
       </c>
       <c r="C22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="73">
         <f>D20-C20</f>
         <v/>
       </c>
@@ -10308,11 +10352,11 @@
           <t>Grades 7-8</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="82">
         <f>'I-FTE'!C22+'I-FTE'!C28</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="82">
         <f>B8/'I-Assumptions'!B9</f>
         <v/>
       </c>
@@ -10327,11 +10371,11 @@
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="82">
         <f>'I-FTE'!C21+'I-FTE'!C27</f>
         <v/>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="82">
         <f>B9/'I-Assumptions'!B10</f>
         <v/>
       </c>
@@ -10346,11 +10390,11 @@
           <t>NET</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="83">
         <f>B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="83">
         <f>C13+C14</f>
         <v/>
       </c>
@@ -10372,7 +10416,7 @@
           <t>Net FTE Saved</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="82">
         <f>-D15</f>
         <v/>
       </c>
@@ -10634,7 +10678,7 @@
           <t>Total Pownal mil rate</t>
         </is>
       </c>
-      <c r="B13" s="53">
+      <c r="B13" s="86">
         <f>'I-Tax'!B9</f>
         <v/>
       </c>
@@ -10645,7 +10689,7 @@
           <t>Pownal RSU share of tax</t>
         </is>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="85">
         <f>'I-Tax'!B10</f>
         <v/>
       </c>
@@ -10683,7 +10727,7 @@
           <t>Low (5%)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="80" t="n">
         <v>0.05</v>
       </c>
       <c r="C16" s="7">
@@ -10705,7 +10749,7 @@
           <t>Mid (10%)</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="80" t="n">
         <v>0.1</v>
       </c>
       <c r="C17" s="7">
@@ -10727,7 +10771,7 @@
           <t>High (15%)</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="80" t="n">
         <v>0.15</v>
       </c>
       <c r="C18" s="7">
@@ -10850,7 +10894,7 @@
           <t>Low (5%)</t>
         </is>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="80" t="n">
         <v>0.05</v>
       </c>
       <c r="C31" s="45">
@@ -10868,7 +10912,7 @@
           <t>Mid (10%)</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="80" t="n">
         <v>0.1</v>
       </c>
       <c r="C32" s="45">
@@ -10886,7 +10930,7 @@
           <t>High (20%)</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="80" t="n">
         <v>0.2</v>
       </c>
       <c r="C33" s="45">
@@ -11010,7 +11054,7 @@
           <t>Low (10%)</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="80" t="n">
         <v>0.1</v>
       </c>
       <c r="C46" s="45">
@@ -11033,7 +11077,7 @@
           <t>Mid (20%)</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="80" t="n">
         <v>0.2</v>
       </c>
       <c r="C47" s="45">
@@ -11056,7 +11100,7 @@
           <t>High (30%)</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="80" t="n">
         <v>0.3</v>
       </c>
       <c r="C48" s="45">
@@ -11284,7 +11328,7 @@
           <t>Path B true net savings (from C-FY28Paths)</t>
         </is>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="73">
         <f>'C-FY28Paths'!B36</f>
         <v/>
       </c>
@@ -11295,7 +11339,7 @@
           <t>Path B MARGINAL savings beyond Path A</t>
         </is>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="73">
         <f>B69-B68</f>
         <v/>
       </c>
@@ -11404,7 +11448,7 @@
           <t>PATH B RISK-ADJUSTED NET (mid scenario)</t>
         </is>
       </c>
-      <c r="B78" s="26">
+      <c r="B78" s="76">
         <f>B69-C76</f>
         <v/>
       </c>
@@ -11440,7 +11484,7 @@
           <t>Path B marginal annual benefit (true net - Path A)</t>
         </is>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="73">
         <f>B70</f>
         <v/>
       </c>
@@ -11462,7 +11506,7 @@
           <t>Break-even period (years)</t>
         </is>
       </c>
-      <c r="B86" s="40">
+      <c r="B86" s="84">
         <f>IF(B84&gt;0,B85/B84,"NEVER")</f>
         <v/>
       </c>
@@ -11501,7 +11545,7 @@
           <t>MS consolidation: transport cost for Freeport 6th to DCS</t>
         </is>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="73">
         <f>'I-Assumptions'!B13*'I-Assumptions'!B12</f>
         <v/>
       </c>
@@ -11517,7 +11561,7 @@
           <t>Community identity: DCS becomes multi-town 6th grade</t>
         </is>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="73">
         <f>0</f>
         <v/>
       </c>
@@ -11533,7 +11577,7 @@
           <t>Additional efficiencies depend on Board action</t>
         </is>
       </c>
-      <c r="B96" s="13">
+      <c r="B96" s="73">
         <f>0</f>
         <v/>
       </c>
@@ -11549,7 +11593,7 @@
           <t>DCS scheduling complexity with Pownal 6th graders</t>
         </is>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="73">
         <f>0</f>
         <v/>
       </c>
@@ -11848,15 +11892,15 @@
           <t>NET POSITION (revenue - consumption)</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="76">
         <f>B19-B18</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="76">
         <f>C19-C18</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="76">
         <f>D19-D18</f>
         <v/>
       </c>
@@ -12003,15 +12047,15 @@
           <t>EQUALIZED NET (consumed - contributed)</t>
         </is>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="76">
         <f>B32-B33</f>
         <v/>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="76">
         <f>C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="76">
         <f>D32-D33</f>
         <v/>
       </c>
@@ -12022,15 +12066,15 @@
           <t>Equalized net per household</t>
         </is>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="76">
         <f>B34/'I-Equity'!B104</f>
         <v/>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="76">
         <f>C34/'I-Equity'!C104</f>
         <v/>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="76">
         <f>D34/'I-Equity'!D104</f>
         <v/>
       </c>
@@ -12132,15 +12176,15 @@
           <t>FORMULA PENALTY (+) or BENEFIT (-)</t>
         </is>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="76">
         <f>B44-B45</f>
         <v/>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="76">
         <f>C44-C45</f>
         <v/>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="76">
         <f>D44-D45</f>
         <v/>
       </c>
@@ -12151,15 +12195,15 @@
           <t>Formula penalty per household</t>
         </is>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="76">
         <f>B46/'I-Equity'!B104</f>
         <v/>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="76">
         <f>C46/'I-Equity'!C104</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="76">
         <f>D46/'I-Equity'!D104</f>
         <v/>
       </c>
@@ -12471,7 +12515,7 @@
           <t>TRUE NET SAVINGS from closing PES (from C-FY28Paths)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="73">
         <f>'C-FY28Paths'!B36</f>
         <v/>
       </c>
@@ -12579,7 +12623,7 @@
           <t>Less: State EPS share (current)</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="73">
         <f>-'I-Withdrawal'!B109</f>
         <v/>
       </c>
@@ -12590,7 +12634,7 @@
           <t>Less: Isolated small school adjustment</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="73">
         <f>-'I-Withdrawal'!B110</f>
         <v/>
       </c>
@@ -12623,7 +12667,7 @@
           <t>CHANGE vs. CURRENT RSU ASSESSMENT</t>
         </is>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="76">
         <f>B29-B31</f>
         <v/>
       </c>
@@ -12634,7 +12678,7 @@
           <t>Percentage increase</t>
         </is>
       </c>
-      <c r="B33" s="55">
+      <c r="B33" s="87">
         <f>B32/B31</f>
         <v/>
       </c>
@@ -12645,7 +12689,7 @@
           <t>New estimated mil rate (education only)</t>
         </is>
       </c>
-      <c r="B35" s="56">
+      <c r="B35" s="88">
         <f>B29/'I-Withdrawal'!B111*1000</f>
         <v/>
       </c>
@@ -12656,7 +12700,7 @@
           <t>Current RSU education mil rate</t>
         </is>
       </c>
-      <c r="B36" s="53">
+      <c r="B36" s="86">
         <f>'I-Withdrawal'!B114</f>
         <v/>
       </c>
@@ -12678,7 +12722,7 @@
           <t>Annual cost change per household (636 homes)</t>
         </is>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="76">
         <f>B32/'I-Withdrawal'!B112</f>
         <v/>
       </c>
@@ -12721,7 +12765,7 @@
           <t>Less: AOS shared services savings</t>
         </is>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="73">
         <f>-'I-Withdrawal'!B57</f>
         <v/>
       </c>
@@ -12732,7 +12776,7 @@
           <t>Less: State EPS + small school adjustment</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="73">
         <f>B27+B28</f>
         <v/>
       </c>
@@ -12754,7 +12798,7 @@
           <t>CHANGE vs. CURRENT RSU ASSESSMENT</t>
         </is>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="76">
         <f>B47-B31</f>
         <v/>
       </c>
@@ -12765,7 +12809,7 @@
           <t>New estimated mil rate (AOS model)</t>
         </is>
       </c>
-      <c r="B49" s="58">
+      <c r="B49" s="89">
         <f>B47/'I-Withdrawal'!B111*1000</f>
         <v/>
       </c>
@@ -12776,7 +12820,7 @@
           <t>Annual cost change per household</t>
         </is>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="76">
         <f>B48/'I-Withdrawal'!B112</f>
         <v/>
       </c>
@@ -12830,7 +12874,7 @@
           <t>Probability of success (analyst assessment)</t>
         </is>
       </c>
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="80" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -12948,7 +12992,7 @@
           <t>Less: State EPS share</t>
         </is>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="73">
         <f>-'I-Withdrawal'!B109</f>
         <v/>
       </c>
@@ -12959,7 +13003,7 @@
           <t>Less: Isolated small school adjustment</t>
         </is>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="73">
         <f>-'I-Withdrawal'!B110</f>
         <v/>
       </c>
@@ -12981,7 +13025,7 @@
           <t>CHANGE vs. CURRENT RSU ASSESSMENT</t>
         </is>
       </c>
-      <c r="B79" s="26">
+      <c r="B79" s="76">
         <f>B77-B31</f>
         <v/>
       </c>
@@ -12992,7 +13036,7 @@
           <t>Annual cost change per household</t>
         </is>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="76">
         <f>B79/'I-Withdrawal'!B112</f>
         <v/>
       </c>
@@ -13003,7 +13047,7 @@
           <t>Mil rate (K-8 model)</t>
         </is>
       </c>
-      <c r="B81" s="58">
+      <c r="B81" s="89">
         <f>B77/'I-Withdrawal'!B111*1000</f>
         <v/>
       </c>
@@ -13014,7 +13058,7 @@
           <t>vs. Scenario B (K-5 + full tuition)</t>
         </is>
       </c>
-      <c r="B82" s="59">
+      <c r="B82" s="90">
         <f>B77-B29</f>
         <v/>
       </c>
@@ -13146,7 +13190,7 @@
           <t>Savings vs RSU: Scenario B (K-5 + tuition)</t>
         </is>
       </c>
-      <c r="B101" s="26">
+      <c r="B101" s="76">
         <f>-B32</f>
         <v/>
       </c>
@@ -13157,7 +13201,7 @@
           <t>Savings vs RSU: Scenario C (K-5 + AOS)</t>
         </is>
       </c>
-      <c r="B102" s="26">
+      <c r="B102" s="76">
         <f>-B48</f>
         <v/>
       </c>
@@ -13168,7 +13212,7 @@
           <t>Savings vs RSU: Scenario E (K-8 + HS tuition)</t>
         </is>
       </c>
-      <c r="B103" s="26">
+      <c r="B103" s="76">
         <f>-B79</f>
         <v/>
       </c>
@@ -13242,11 +13286,11 @@
         <f>B29*1.035</f>
         <v/>
       </c>
-      <c r="D111" s="13">
+      <c r="D111" s="73">
         <f>C111-B111</f>
         <v/>
       </c>
-      <c r="E111" s="13">
+      <c r="E111" s="73">
         <f>D111+'I-Withdrawal'!B91</f>
         <v/>
       </c>
@@ -13265,11 +13309,11 @@
         <f>C111*1.035</f>
         <v/>
       </c>
-      <c r="D112" s="13">
+      <c r="D112" s="73">
         <f>C112-B112</f>
         <v/>
       </c>
-      <c r="E112" s="13">
+      <c r="E112" s="73">
         <f>E111+D112</f>
         <v/>
       </c>
@@ -13288,11 +13332,11 @@
         <f>C112*1.035</f>
         <v/>
       </c>
-      <c r="D113" s="13">
+      <c r="D113" s="73">
         <f>C113-B113</f>
         <v/>
       </c>
-      <c r="E113" s="13">
+      <c r="E113" s="73">
         <f>E112+D113</f>
         <v/>
       </c>
@@ -13311,11 +13355,11 @@
         <f>C113*1.035</f>
         <v/>
       </c>
-      <c r="D114" s="13">
+      <c r="D114" s="73">
         <f>C114-B114</f>
         <v/>
       </c>
-      <c r="E114" s="13">
+      <c r="E114" s="73">
         <f>E113+D114</f>
         <v/>
       </c>
@@ -13334,11 +13378,11 @@
         <f>C114*1.035</f>
         <v/>
       </c>
-      <c r="D115" s="13">
+      <c r="D115" s="73">
         <f>C115-B115</f>
         <v/>
       </c>
-      <c r="E115" s="13">
+      <c r="E115" s="73">
         <f>E114+D115</f>
         <v/>
       </c>
@@ -13349,7 +13393,7 @@
           <t>5-YEAR CUMULATIVE COST OF INDEPENDENCE</t>
         </is>
       </c>
-      <c r="B116" s="26">
+      <c r="B116" s="76">
         <f>E115</f>
         <v/>
       </c>
@@ -13407,21 +13451,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALC: Legal &amp; Strategic Analysis</t>
+          <t>CALC: Legal Options Analysis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Structured assessment of Pownal's legal options. Not formula-heavy;</t>
+          <t>Assessment of legal pathways available under Maine education law.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>provides decision framework for qualitative dimensions.</t>
+          <t>Provides decision framework for evaluating options objectively.</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13912,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Leverage (threaten withdrawal)</t>
+          <t>Withdrawal as negotiation context</t>
         </is>
       </c>
       <c r="B32" s="45" t="n">
@@ -14351,35 +14395,35 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>STRATEGY: Initiate §1512 challenge AND withdrawal petition simultaneously.</t>
+          <t>NOTE: Both §1512 challenge and §1466 withdrawal can be pursued concurrently.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>If §1512 challenge succeeds -&gt; withdrawal becomes unnecessary leverage.</t>
+          <t>If §1512 challenge clarifies the legal question, withdrawal may become unnecessary.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>If §1512 challenge fails -&gt; withdrawal is already underway as backup.</t>
+          <t>If §1512 challenge does not succeed, withdrawal remains available as an alternative.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>PART 5: RECOMMENDED STRATEGY</t>
+          <t>PART 5: OPTIONS ANALYSIS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="68" t="inlineStr">
         <is>
-          <t>PHASE 1 (Immediate): Retain education law counsel. File petition for §1512</t>
+          <t>OPTION 1 (Legal Clarification): Retain education law counsel. File petition for §1512</t>
         </is>
       </c>
     </row>
@@ -14393,91 +14437,91 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and creates public record of Pownal's objection.</t>
+          <t xml:space="preserve">   and creates a public record of the community's position.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="68" t="inlineStr">
         <is>
-          <t>PHASE 2 (Concurrent): Begin §1466 withdrawal petition. Collect signatures,</t>
+          <t>OPTION 2 (Withdrawal Process): Begin §1466 withdrawal petition. Collect signatures,</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   hold town vote to authorize committee and $50K. This is the credible threat.</t>
+          <t xml:space="preserve">   hold town vote to authorize committee and $50K. This initiates a formal process</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Even if Pownal doesn't ultimately withdraw, the process forces RSU 5 to</t>
+          <t xml:space="preserve">   that requires RSU 5 to engage in negotiation. The withdrawal process is</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   negotiate seriously. Freeport's 2014 attempt (failed by 76 votes) proves</t>
+          <t xml:space="preserve">   fully reversible until the final referendum vote.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   withdrawal is a realistic possibility in this district.</t>
+          <t xml:space="preserve">   Freeport's 2014 attempt (failed by 76 votes) demonstrates the process works.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="68" t="inlineStr">
         <is>
-          <t>PHASE 3 (Conditional): If RSU 5 Board abandons Option 2 (as SAD 75 did for</t>
+          <t>OPTION 3 (Conditional): If RSU 5 Board changes course on restructuring</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Harpswell), withdrawal process can be paused or terminated at any point.</t>
+          <t xml:space="preserve">   (as SAD 75 did for Harpswell), the withdrawal process can be paused</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   If Board proceeds, complete withdrawal agreement by Nov 30 deadline.</t>
+          <t xml:space="preserve">   or terminated at any point before the final referendum.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="68" t="inlineStr">
         <is>
-          <t>KEY INSIGHT: The withdrawal process is fully reversible until the final</t>
+          <t>KEY CONSIDERATIONS: The withdrawal process is fully reversible until the final</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   referendum vote. Starting it costs ~$50K but creates enormous leverage.</t>
+          <t xml:space="preserve">   referendum vote. Starting it costs ~$50K and initiates formal negotiation.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   NOT starting it leaves Pownal with no reliable legal defense against</t>
+          <t xml:space="preserve">   Not starting it limits Pownal's options to §1512 and formula advocacy,</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Option 2 as framed.</t>
+          <t xml:space="preserve">   both of which require Board cooperation.</t>
         </is>
       </c>
     </row>
@@ -14485,8 +14529,8 @@
   <mergeCells count="9">
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A8:E8"/>
@@ -14569,11 +14613,11 @@
           <t>PES (Pownal Elementary)</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="82">
         <f>'I-DOEStaffing'!B11</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="82">
         <f>'I-DOEStaffing'!L11</f>
         <v/>
       </c>
@@ -14592,11 +14636,11 @@
           <t>DCS (Durham Community)</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="82">
         <f>'I-DOEStaffing'!B12</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="82">
         <f>'I-DOEStaffing'!L12</f>
         <v/>
       </c>
@@ -14615,11 +14659,11 @@
           <t>MSS (Morse Street)</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="82">
         <f>'I-DOEStaffing'!B13</f>
         <v/>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="82">
         <f>'I-DOEStaffing'!L13</f>
         <v/>
       </c>
@@ -14638,11 +14682,11 @@
           <t>MLS (Mast Landing)</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="82">
         <f>'I-DOEStaffing'!B14</f>
         <v/>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="82">
         <f>'I-DOEStaffing'!L14</f>
         <v/>
       </c>
@@ -14661,11 +14705,11 @@
           <t>FMS (Freeport Middle)</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="82">
         <f>'I-DOEStaffing'!B15</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="82">
         <f>'I-DOEStaffing'!L15</f>
         <v/>
       </c>
@@ -14684,11 +14728,11 @@
           <t>FHS (Freeport High)</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="82">
         <f>'I-DOEStaffing'!B16</f>
         <v/>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="82">
         <f>'I-DOEStaffing'!L16</f>
         <v/>
       </c>
@@ -14707,11 +14751,11 @@
           <t>District-wide (central)</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="82">
         <f>'I-DOEStaffing'!B17</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="82">
         <f>'I-DOEStaffing'!L17</f>
         <v/>
       </c>
@@ -14730,11 +14774,11 @@
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="83">
         <f>'I-DOEStaffing'!B18</f>
         <v/>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="83">
         <f>'I-DOEStaffing'!L18</f>
         <v/>
       </c>
@@ -14787,15 +14831,15 @@
       <c r="A20" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="82">
         <f>'I-DOEStaffing'!B11</f>
         <v/>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="82">
         <f>'I-DOEStaffing'!B18</f>
         <v/>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="85">
         <f>B20/C20</f>
         <v/>
       </c>
@@ -14804,15 +14848,15 @@
       <c r="A21" s="6" t="n">
         <v>2017</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="82">
         <f>'I-DOEStaffing'!C11</f>
         <v/>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="82">
         <f>'I-DOEStaffing'!C18</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="85">
         <f>B21/C21</f>
         <v/>
       </c>
@@ -14821,15 +14865,15 @@
       <c r="A22" s="6" t="n">
         <v>2018</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="82">
         <f>'I-DOEStaffing'!D11</f>
         <v/>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="82">
         <f>'I-DOEStaffing'!D18</f>
         <v/>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="85">
         <f>B22/C22</f>
         <v/>
       </c>
@@ -14838,15 +14882,15 @@
       <c r="A23" s="6" t="n">
         <v>2019</v>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="82">
         <f>'I-DOEStaffing'!E11</f>
         <v/>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="82">
         <f>'I-DOEStaffing'!E18</f>
         <v/>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="85">
         <f>B23/C23</f>
         <v/>
       </c>
@@ -14855,15 +14899,15 @@
       <c r="A24" s="6" t="n">
         <v>2020</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="82">
         <f>'I-DOEStaffing'!F11</f>
         <v/>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="82">
         <f>'I-DOEStaffing'!F18</f>
         <v/>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="85">
         <f>B24/C24</f>
         <v/>
       </c>
@@ -14872,15 +14916,15 @@
       <c r="A25" s="6" t="n">
         <v>2021</v>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="82">
         <f>'I-DOEStaffing'!G11</f>
         <v/>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="82">
         <f>'I-DOEStaffing'!G18</f>
         <v/>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="85">
         <f>B25/C25</f>
         <v/>
       </c>
@@ -14889,15 +14933,15 @@
       <c r="A26" s="6" t="n">
         <v>2022</v>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="82">
         <f>'I-DOEStaffing'!H11</f>
         <v/>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="82">
         <f>'I-DOEStaffing'!H18</f>
         <v/>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="85">
         <f>B26/C26</f>
         <v/>
       </c>
@@ -14906,15 +14950,15 @@
       <c r="A27" s="6" t="n">
         <v>2023</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="82">
         <f>'I-DOEStaffing'!I11</f>
         <v/>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="82">
         <f>'I-DOEStaffing'!I18</f>
         <v/>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="85">
         <f>B27/C27</f>
         <v/>
       </c>
@@ -14923,15 +14967,15 @@
       <c r="A28" s="6" t="n">
         <v>2024</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B28" s="82">
         <f>'I-DOEStaffing'!J11</f>
         <v/>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="82">
         <f>'I-DOEStaffing'!J18</f>
         <v/>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="85">
         <f>B28/C28</f>
         <v/>
       </c>
@@ -14940,15 +14984,15 @@
       <c r="A29" s="6" t="n">
         <v>2025</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="82">
         <f>'I-DOEStaffing'!K11</f>
         <v/>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="82">
         <f>'I-DOEStaffing'!K18</f>
         <v/>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="85">
         <f>B29/C29</f>
         <v/>
       </c>
@@ -14957,15 +15001,15 @@
       <c r="A30" s="6" t="n">
         <v>2026</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="82">
         <f>'I-DOEStaffing'!L11</f>
         <v/>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="82">
         <f>'I-DOEStaffing'!L18</f>
         <v/>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="85">
         <f>B30/C30</f>
         <v/>
       </c>
@@ -14984,7 +15028,7 @@
         <f>SUM('I-Enrollment'!F10:'I-Enrollment'!F15)</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="77">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -15047,11 +15091,11 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="82">
         <f>'I-DOEStaffing'!B23+'I-DOEStaffing'!B43+'I-DOEStaffing'!B33</f>
         <v/>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="82">
         <f>'I-DOEStaffing'!L23+'I-DOEStaffing'!L43+'I-DOEStaffing'!L33</f>
         <v/>
       </c>
@@ -15070,11 +15114,11 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B39" s="35">
+      <c r="B39" s="82">
         <f>'I-DOEStaffing'!B24+'I-DOEStaffing'!B44+'I-DOEStaffing'!B34</f>
         <v/>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="82">
         <f>'I-DOEStaffing'!L24+'I-DOEStaffing'!L44+'I-DOEStaffing'!L34</f>
         <v/>
       </c>
@@ -15093,11 +15137,11 @@
           <t>MSS</t>
         </is>
       </c>
-      <c r="B40" s="35">
+      <c r="B40" s="82">
         <f>'I-DOEStaffing'!B25+'I-DOEStaffing'!B45+'I-DOEStaffing'!B35</f>
         <v/>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="82">
         <f>'I-DOEStaffing'!L25+'I-DOEStaffing'!L45+'I-DOEStaffing'!L35</f>
         <v/>
       </c>
@@ -15116,11 +15160,11 @@
           <t>MLS</t>
         </is>
       </c>
-      <c r="B41" s="35">
+      <c r="B41" s="82">
         <f>'I-DOEStaffing'!B26+'I-DOEStaffing'!B46+'I-DOEStaffing'!B36</f>
         <v/>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="82">
         <f>'I-DOEStaffing'!L26+'I-DOEStaffing'!L46+'I-DOEStaffing'!L36</f>
         <v/>
       </c>
@@ -15139,11 +15183,11 @@
           <t>FMS</t>
         </is>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="82">
         <f>'I-DOEStaffing'!B27+'I-DOEStaffing'!B47+'I-DOEStaffing'!B37</f>
         <v/>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="82">
         <f>'I-DOEStaffing'!L27+'I-DOEStaffing'!L47+'I-DOEStaffing'!L37</f>
         <v/>
       </c>
@@ -15162,11 +15206,11 @@
           <t>FHS</t>
         </is>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="82">
         <f>'I-DOEStaffing'!B28+'I-DOEStaffing'!B48+'I-DOEStaffing'!B38</f>
         <v/>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="82">
         <f>'I-DOEStaffing'!L28+'I-DOEStaffing'!L48+'I-DOEStaffing'!L38</f>
         <v/>
       </c>
@@ -15219,11 +15263,11 @@
       <c r="A49" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="B49" s="35">
+      <c r="B49" s="82">
         <f>'I-DOEStaffing'!B33</f>
         <v/>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="82">
         <f>AVERAGE('I-DOEStaffing'!B34,'I-DOEStaffing'!B35,'I-DOEStaffing'!B36)</f>
         <v/>
       </c>
@@ -15236,11 +15280,11 @@
       <c r="A50" s="6" t="n">
         <v>2017</v>
       </c>
-      <c r="B50" s="35">
+      <c r="B50" s="82">
         <f>'I-DOEStaffing'!C33</f>
         <v/>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="82">
         <f>AVERAGE('I-DOEStaffing'!C34,'I-DOEStaffing'!C35,'I-DOEStaffing'!C36)</f>
         <v/>
       </c>
@@ -15253,11 +15297,11 @@
       <c r="A51" s="6" t="n">
         <v>2018</v>
       </c>
-      <c r="B51" s="35">
+      <c r="B51" s="82">
         <f>'I-DOEStaffing'!D33</f>
         <v/>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="82">
         <f>AVERAGE('I-DOEStaffing'!D34,'I-DOEStaffing'!D35,'I-DOEStaffing'!D36)</f>
         <v/>
       </c>
@@ -15270,11 +15314,11 @@
       <c r="A52" s="6" t="n">
         <v>2019</v>
       </c>
-      <c r="B52" s="35">
+      <c r="B52" s="82">
         <f>'I-DOEStaffing'!E33</f>
         <v/>
       </c>
-      <c r="C52" s="35">
+      <c r="C52" s="82">
         <f>AVERAGE('I-DOEStaffing'!E34,'I-DOEStaffing'!E35,'I-DOEStaffing'!E36)</f>
         <v/>
       </c>
@@ -15287,11 +15331,11 @@
       <c r="A53" s="6" t="n">
         <v>2020</v>
       </c>
-      <c r="B53" s="35">
+      <c r="B53" s="82">
         <f>'I-DOEStaffing'!F33</f>
         <v/>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="82">
         <f>AVERAGE('I-DOEStaffing'!F34,'I-DOEStaffing'!F35,'I-DOEStaffing'!F36)</f>
         <v/>
       </c>
@@ -15304,11 +15348,11 @@
       <c r="A54" s="6" t="n">
         <v>2021</v>
       </c>
-      <c r="B54" s="35">
+      <c r="B54" s="82">
         <f>'I-DOEStaffing'!G33</f>
         <v/>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="82">
         <f>AVERAGE('I-DOEStaffing'!G34,'I-DOEStaffing'!G35,'I-DOEStaffing'!G36)</f>
         <v/>
       </c>
@@ -15321,11 +15365,11 @@
       <c r="A55" s="6" t="n">
         <v>2022</v>
       </c>
-      <c r="B55" s="35">
+      <c r="B55" s="82">
         <f>'I-DOEStaffing'!H33</f>
         <v/>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="82">
         <f>AVERAGE('I-DOEStaffing'!H34,'I-DOEStaffing'!H35,'I-DOEStaffing'!H36)</f>
         <v/>
       </c>
@@ -15338,11 +15382,11 @@
       <c r="A56" s="6" t="n">
         <v>2023</v>
       </c>
-      <c r="B56" s="35">
+      <c r="B56" s="82">
         <f>'I-DOEStaffing'!I33</f>
         <v/>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="82">
         <f>AVERAGE('I-DOEStaffing'!I34,'I-DOEStaffing'!I35,'I-DOEStaffing'!I36)</f>
         <v/>
       </c>
@@ -15355,11 +15399,11 @@
       <c r="A57" s="6" t="n">
         <v>2024</v>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="82">
         <f>'I-DOEStaffing'!J33</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="82">
         <f>AVERAGE('I-DOEStaffing'!J34,'I-DOEStaffing'!J35,'I-DOEStaffing'!J36)</f>
         <v/>
       </c>
@@ -15372,11 +15416,11 @@
       <c r="A58" s="6" t="n">
         <v>2025</v>
       </c>
-      <c r="B58" s="35">
+      <c r="B58" s="82">
         <f>'I-DOEStaffing'!K33</f>
         <v/>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="82">
         <f>AVERAGE('I-DOEStaffing'!K34,'I-DOEStaffing'!K35,'I-DOEStaffing'!K36)</f>
         <v/>
       </c>
@@ -15389,11 +15433,11 @@
       <c r="A59" s="6" t="n">
         <v>2026</v>
       </c>
-      <c r="B59" s="35">
+      <c r="B59" s="82">
         <f>'I-DOEStaffing'!L33</f>
         <v/>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="82">
         <f>AVERAGE('I-DOEStaffing'!L34,'I-DOEStaffing'!L35,'I-DOEStaffing'!L36)</f>
         <v/>
       </c>
@@ -15456,11 +15500,11 @@
           <t>PES</t>
         </is>
       </c>
-      <c r="B65" s="35">
+      <c r="B65" s="82">
         <f>'I-DOEStaffing'!L23</f>
         <v/>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="82">
         <f>'I-FTE'!D10</f>
         <v/>
       </c>
@@ -15480,11 +15524,11 @@
           <t>DCS</t>
         </is>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="82">
         <f>'I-DOEStaffing'!L24</f>
         <v/>
       </c>
-      <c r="C66" s="35">
+      <c r="C66" s="82">
         <f>'I-FTE'!D11</f>
         <v/>
       </c>
@@ -15633,7 +15677,7 @@
           <t>MS consolidation teacher savings</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="73">
         <f>-'C-MSConsol'!B21</f>
         <v/>
       </c>
@@ -15649,7 +15693,7 @@
           <t>DCS admin change (multi-community K-6)</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="73">
         <f>0</f>
         <v/>
       </c>
@@ -15665,7 +15709,7 @@
           <t>Freeport 6th transportation</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="73">
         <f>'I-Assumptions'!B13*'I-Assumptions'!B12</f>
         <v/>
       </c>
@@ -15681,7 +15725,7 @@
           <t>DCS portable classrooms</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="73">
         <f>0</f>
         <v/>
       </c>
@@ -15697,7 +15741,7 @@
           <t>Additional efficiencies (midpoint)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="73">
         <f>-AVERAGE('I-Assumptions'!B22,'I-Assumptions'!B23)</f>
         <v/>
       </c>
@@ -15755,7 +15799,7 @@
           <t>PES instruction eliminated (gross)</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="73">
         <f>-('C-Budget'!D7-'I-Budget'!D14)</f>
         <v/>
       </c>
@@ -15771,7 +15815,7 @@
           <t>Transport: Pownal K-6 to DCS</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="73">
         <f>'I-Assumptions'!B14*'I-Assumptions'!B12</f>
         <v/>
       </c>
@@ -15787,7 +15831,7 @@
           <t>Transport: Freeport PreK to PES</t>
         </is>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="73">
         <f>'I-Assumptions'!B15*'I-Assumptions'!B12</f>
         <v/>
       </c>
@@ -15803,7 +15847,7 @@
           <t>Transport: Durham PreK to PES</t>
         </is>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="73">
         <f>'I-Assumptions'!B16*'I-Assumptions'!B12</f>
         <v/>
       </c>
@@ -15819,7 +15863,7 @@
           <t>DCS multi-community coordination</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="73">
         <f>'I-Assumptions'!B20</f>
         <v/>
       </c>
@@ -15835,7 +15879,7 @@
           <t>PES full EC conversion (amortized)</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="73">
         <f>'I-Assumptions'!B17*'I-Assumptions'!B18/'I-Assumptions'!B19</f>
         <v/>
       </c>
@@ -15951,7 +15995,7 @@
           <t>Minus transport (Path B)</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="73">
         <f>-SUM(B19:B21)</f>
         <v/>
       </c>
@@ -15962,7 +16006,7 @@
           <t>Minus PES conversion (amortized)</t>
         </is>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="73">
         <f>-B23</f>
         <v/>
       </c>
@@ -15973,7 +16017,7 @@
           <t>TRUE NET SAVINGS FROM CLOSING PES</t>
         </is>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="76">
         <f>B33+B34+B35</f>
         <v/>
       </c>
@@ -16032,15 +16076,15 @@
           <t>Increase from FY27 adopted</t>
         </is>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="77">
         <f>(B40-'C-FY28Projection'!B7)/'C-FY28Projection'!B7</f>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="77">
         <f>(C40-'C-FY28Projection'!B7)/'C-FY28Projection'!B7</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="77">
         <f>(D40-'C-FY28Projection'!B7)/'C-FY28Projection'!B7</f>
         <v/>
       </c>
@@ -16081,7 +16125,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="76">
         <f>B36</f>
         <v/>
       </c>
@@ -16098,7 +16142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16632,6 +16676,5406 @@
       <c r="B47" s="72" t="inlineStr">
         <is>
           <t>Maine DOE NEO Staff Historical Data (Dec 1, 2015-2025). Dataset: [Fed_Reporting].Reports.StaffHistoricalDec1, SAUOrgId=1449. Requested by Mark Dohle (03/04/2026), fulfilled by Maine DOE Data Team (Trevor R. Burns, 03/09/2026). DOE Helpdesk Issue #66636. File: 'MDohle RSU 5 Staff by FTE.xlsx'. Public use; FTE headcounts reported as of December 1 each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>NEW CALCULATION SHEETS (added for audit traceability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>[Fn 64]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RSU 5 Board of Directors, Feb 25, 2026. Voted 11-0 for $100K facilities study from Capital Reserves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>[Fn 65]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PDT Architects / FHS Advisory Committee, Jan 2013. FHS renovation: $16.95M for 650-student building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C-SchoolBudgets</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>In Overview workbook. Cross-year school budget comparison FY22-FY27. Sources: I-BudgetData from each FY workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C-PathC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Path C formula reform: 7 valuation/enrollment split scenarios. Inputs: I-Revenue, I-Equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C-PathD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Path D redistricting: PES cost at enrollment levels 105-180. Inputs: I-Budget, I-Enrollment, I-Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C-Capacity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>School capacity/utilization for all 6 schools. Sources: C-PESPreservation, I-Withdrawal, PDT study, peak enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C-FacilitiesRisk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MSS deferred maintenance inventory + major renovation estimate. Sources: FC capital plans 2015-2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C-RSUImpact</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RSU 5 impact if Pownal withdraws: revenue/cost/shortfall model. Sources: I-Revenue, I-Budget, C-Consumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="91" t="inlineStr">
+        <is>
+          <t>C-EducationQuality</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Educational quality analysis: state assessment data, facility suitability, Ch. 124 compliance, consolidation research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Proficiency data: US News (2024-25 profiles), GreatSchools (2024-25 ratings), NeighborhoodScout (Maine DOE 2023-24).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Facility data: RSU 5 FC minutes (2016-2023), DCS design (SchoolDesigns.com/Harriman), Ch. 124 (05 CMR 071-124-9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Research: Krueger (1999), Chetty et al (2011), Heinesen (2022, IZA), Coulson &amp; Bhatt (2022), Cooley &amp; Floyd (2013).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: Path C - Cost-Sharing Formula Reform Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models the impact of changing ALM allocation from current fixed percentages to various valuation/enrollment splits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All inputs from I-Revenue and I-Equity. Formula: ALM_town = (val_weight * val_share + enroll_weight * enroll_share) * total_ALM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. INPUTS (from I-Revenue, I-Equity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total ALM (FY27)</t>
+        </is>
+      </c>
+      <c r="B6" s="92" t="n">
+        <v>17388716.98</v>
+      </c>
+      <c r="C6" s="93" t="inlineStr">
+        <is>
+          <t>Sum of town ALMs from I-Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pownal state valuation share</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Row 60: 399,866,667 / 3,603,433,334</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Durham state valuation share</t>
+        </is>
+      </c>
+      <c r="B9" s="94" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="C9" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Row 60: 692,816,667 / 3,603,433,334</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Freeport state valuation share</t>
+        </is>
+      </c>
+      <c r="B10" s="94" t="n">
+        <v>0.6967</v>
+      </c>
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Row 60: 2,510,750,000 / 3,603,433,334</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pownal enrollment share</t>
+        </is>
+      </c>
+      <c r="B12" s="94" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Rows 24-27: 205 / 1970</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Durham enrollment share</t>
+        </is>
+      </c>
+      <c r="B13" s="94" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="C13" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Rows 24-27: 692 / 1970</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Freeport enrollment share</t>
+        </is>
+      </c>
+      <c r="B14" s="94" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="C14" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity Rows 24-27: 1073 / 1970</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pownal actual ALM (FY27)</t>
+        </is>
+      </c>
+      <c r="B16" s="92" t="n">
+        <v>2190978.34</v>
+      </c>
+      <c r="C16" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Durham actual ALM (FY27)</t>
+        </is>
+      </c>
+      <c r="B17" s="92" t="n">
+        <v>3724663.18</v>
+      </c>
+      <c r="C17" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Freeport actual ALM (FY27)</t>
+        </is>
+      </c>
+      <c r="B18" s="92" t="n">
+        <v>11473075.46</v>
+      </c>
+      <c r="C18" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pownal actual ALM share</t>
+        </is>
+      </c>
+      <c r="B20" s="94" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="C20" s="93" t="inlineStr">
+        <is>
+          <t>Pownal ALM / Total ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durham actual ALM share</t>
+        </is>
+      </c>
+      <c r="B21" s="94" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="C21" s="93" t="inlineStr">
+        <is>
+          <t>Durham ALM / Total ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Freeport actual ALM share</t>
+        </is>
+      </c>
+      <c r="B22" s="94" t="n">
+        <v>0.6598000000000001</v>
+      </c>
+      <c r="C22" s="93" t="inlineStr">
+        <is>
+          <t>Freeport ALM / Total ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>2. FORMULA SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Formula: New ALM = (val_weight * val_share + enroll_weight * enroll_share) * total_ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Change = New ALM - Current ALM. Negative = savings for that town.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B28" s="91" t="inlineStr">
+        <is>
+          <t>Val Weight</t>
+        </is>
+      </c>
+      <c r="C28" s="91" t="inlineStr">
+        <is>
+          <t>Enroll Weight</t>
+        </is>
+      </c>
+      <c r="D28" s="91" t="inlineStr">
+        <is>
+          <t>Pownal New ALM</t>
+        </is>
+      </c>
+      <c r="E28" s="91" t="inlineStr">
+        <is>
+          <t>Durham New ALM</t>
+        </is>
+      </c>
+      <c r="F28" s="91" t="inlineStr">
+        <is>
+          <t>Freeport New ALM</t>
+        </is>
+      </c>
+      <c r="G28" s="91" t="inlineStr">
+        <is>
+          <t>Pownal Change</t>
+        </is>
+      </c>
+      <c r="H28" s="91" t="inlineStr">
+        <is>
+          <t>Durham Change</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="inlineStr">
+        <is>
+          <t>Freeport Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current (fixed %)</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>2190978</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>3724663</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>11473075</v>
+      </c>
+      <c r="G29" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>85/15 (FC recommendation)</t>
+        </is>
+      </c>
+      <c r="B30" s="96" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C30" s="96" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>1912150</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>3758571</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>11718256</v>
+      </c>
+      <c r="G30" s="95" t="n">
+        <v>-278828</v>
+      </c>
+      <c r="H30" s="95" t="n">
+        <v>33908</v>
+      </c>
+      <c r="I30" s="95" t="n">
+        <v>245181</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>75/25</t>
+        </is>
+      </c>
+      <c r="B31" s="96" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C31" s="96" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>1900152</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>4035052</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>11453948</v>
+      </c>
+      <c r="G31" s="95" t="n">
+        <v>-290826</v>
+      </c>
+      <c r="H31" s="95" t="n">
+        <v>310389</v>
+      </c>
+      <c r="I31" s="95" t="n">
+        <v>-19128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>60/40</t>
+        </is>
+      </c>
+      <c r="B32" s="96" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C32" s="96" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>1882155</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>4449773</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>11057485</v>
+      </c>
+      <c r="G32" s="95" t="n">
+        <v>-308824</v>
+      </c>
+      <c r="H32" s="95" t="n">
+        <v>725109</v>
+      </c>
+      <c r="I32" s="95" t="n">
+        <v>-415590</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>50/50</t>
+        </is>
+      </c>
+      <c r="B33" s="96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>1870157</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>4726253</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>10793177</v>
+      </c>
+      <c r="G33" s="95" t="n">
+        <v>-320822</v>
+      </c>
+      <c r="H33" s="95" t="n">
+        <v>1001590</v>
+      </c>
+      <c r="I33" s="95" t="n">
+        <v>-679899</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>25/75</t>
+        </is>
+      </c>
+      <c r="B34" s="96" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C34" s="96" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>1840161</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>5417455</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>10132405</v>
+      </c>
+      <c r="G34" s="95" t="n">
+        <v>-350817</v>
+      </c>
+      <c r="H34" s="95" t="n">
+        <v>1692792</v>
+      </c>
+      <c r="I34" s="95" t="n">
+        <v>-1340670</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0/100 (pure enrollment)</t>
+        </is>
+      </c>
+      <c r="B35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>1810165</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>6108656</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>9471634</v>
+      </c>
+      <c r="G35" s="95" t="n">
+        <v>-380813</v>
+      </c>
+      <c r="H35" s="95" t="n">
+        <v>2383993</v>
+      </c>
+      <c r="I35" s="95" t="n">
+        <v>-2001441</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>3. COMBINED WITH PATH A (RSU-wide savings $479K-$804K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Net assessment change = Formula change + (Path A savings * town ALM share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Only 85/15 + Path A produces net decreases for ALL three towns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B40" s="91" t="inlineStr">
+        <is>
+          <t>Pownal</t>
+        </is>
+      </c>
+      <c r="C40" s="91" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D40" s="91" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>85/15 + Path A (low $479K)</t>
+        </is>
+      </c>
+      <c r="B41" s="95" t="n">
+        <v>-339182</v>
+      </c>
+      <c r="C41" s="95" t="n">
+        <v>-68694</v>
+      </c>
+      <c r="D41" s="95" t="n">
+        <v>-70863</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>85/15 + Path A (high $804K)</t>
+        </is>
+      </c>
+      <c r="B42" s="95" t="n">
+        <v>-380132</v>
+      </c>
+      <c r="C42" s="95" t="n">
+        <v>-138309</v>
+      </c>
+      <c r="D42" s="95" t="n">
+        <v>-285298</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t>4. TOTAL CONTRIBUTION INCLUDING STATE AID</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Demonstrates near-proportionality when state aid is counted as fair contribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="91" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>Pownal</t>
+        </is>
+      </c>
+      <c r="C46" s="91" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="E46" s="91" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RLC (state-set)</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>2257247</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>3910950</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>14173184</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>20341381</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ALM (RSU formula)</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>2190978</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>3724663</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>11473075</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>17388716</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>State Aid</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>567180</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>5991564</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>1463889</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>8022633</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total contribution</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>5015405</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>13627177</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>27110148</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>45752730</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>% of total funding</t>
+        </is>
+      </c>
+      <c r="B51" s="94" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="C51" s="94" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="D51" s="94" t="n">
+        <v>0.5926</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>% of students</t>
+        </is>
+      </c>
+      <c r="B52" s="94" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="C52" s="94" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="D52" s="94" t="n">
+        <v>0.5447</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gap (funding - enrollment)</t>
+        </is>
+      </c>
+      <c r="B53" s="94" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="C53" s="94" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="D53" s="94" t="n">
+        <v>0.0479</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Total per student</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>24465</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>19693</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>25266</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Sections 2.5, 2.6, 5.1, 5.2, 5.5, Executive Summary.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: Path D - Attendance Zone Redistricting Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models per-student cost changes at PES as enrollment increases through redistricting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fixed costs (~$700K-$800K) do not change with moderate enrollment increases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PES FY27 direct budget</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>2270105</v>
+      </c>
+      <c r="C6" s="93" t="inlineStr">
+        <is>
+          <t>I-Budget: sum of PES articles 1+2+4+5+7+9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PES FY27 enrollment</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>105</v>
+      </c>
+      <c r="C7" s="93" t="inlineStr">
+        <is>
+          <t>I-Enrollment</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PES design capacity</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>C-PESPreservation Row 87; Superintendent estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PES current per-student cost</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>21620</v>
+      </c>
+      <c r="C9" s="93" t="inlineStr">
+        <is>
+          <t>Budget / Enrollment = 2,270,105 / 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>District elementary avg per-student</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>17517</v>
+      </c>
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>C-CostPremium: average of DCS, MSS, MLS per-student</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PES fixed costs (est.)</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C11" s="93" t="inlineStr">
+        <is>
+          <t>Principal + admin + custodian + nurse + building ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PES variable cost per additional student</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>Incremental instruction + materials, from I-Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="91" t="inlineStr">
+        <is>
+          <t>2. ENROLLMENT SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Methodology: Est. Budget = Current Budget + (Added Students x Variable Cost Per Student)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Per-Student Cost = Est. Budget / Target Enrollment</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Premium = Per-Student Cost - District Elementary Average ($17,517)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>Enrollment</t>
+        </is>
+      </c>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>Added Students</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr">
+        <is>
+          <t>Est. Budget</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="inlineStr">
+        <is>
+          <t>Per-Student Cost</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>vs. District Avg</t>
+        </is>
+      </c>
+      <c r="F18" s="91" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>2270105</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>21620</v>
+      </c>
+      <c r="E19" s="95" t="n">
+        <v>4103</v>
+      </c>
+      <c r="F19" s="96" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>2317605</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>21069</v>
+      </c>
+      <c r="E20" s="95" t="n">
+        <v>3552</v>
+      </c>
+      <c r="F20" s="96" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115</v>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>2365105</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>20566</v>
+      </c>
+      <c r="E21" s="95" t="n">
+        <v>3049</v>
+      </c>
+      <c r="F21" s="96" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120</v>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>2412605</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>20105</v>
+      </c>
+      <c r="E22" s="95" t="n">
+        <v>2588</v>
+      </c>
+      <c r="F22" s="96" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>2460105</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>19681</v>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>2164</v>
+      </c>
+      <c r="F23" s="96" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130</v>
+      </c>
+      <c r="B24" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>2507605</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>19289</v>
+      </c>
+      <c r="E24" s="95" t="n">
+        <v>1772</v>
+      </c>
+      <c r="F24" s="96" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135</v>
+      </c>
+      <c r="B25" t="n">
+        <v>30</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>2555105</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>18927</v>
+      </c>
+      <c r="E25" s="95" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F25" s="96" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>150</v>
+      </c>
+      <c r="B26" t="n">
+        <v>45</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>2697605</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>17984</v>
+      </c>
+      <c r="E26" s="95" t="n">
+        <v>467</v>
+      </c>
+      <c r="F26" s="96" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>180</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>2982605</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>16570</v>
+      </c>
+      <c r="E27" s="95" t="n">
+        <v>-947</v>
+      </c>
+      <c r="F27" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>3. KEY FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>At 120 students (+15), PES per-student cost reaches district elementary average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>At 135 students (+30), PES becomes one of the most efficient elementaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Variable cost per additional student (~$9,500) is well below district average (~$17,500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>because fixed costs (principal, building, nurse) are already fully funded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Section 2.7, Executive Summary.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: School Capacity and Utilization Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Estimates design capacity from documented sources, peak enrollment, and classroom counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Formal capacity figures await the $100K facilities study (approved Feb 2026, Board vote 11-0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. CAPACITY ESTIMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>Grades</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="inlineStr">
+        <is>
+          <t>Est. Design Capacity</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
+        <is>
+          <t>Capacity Source</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>FY27 Enrollment</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+      <c r="G6" s="91" t="inlineStr">
+        <is>
+          <t>Spare Seats</t>
+        </is>
+      </c>
+      <c r="H6" s="91" t="inlineStr">
+        <is>
+          <t>Peak Enrollment</t>
+        </is>
+      </c>
+      <c r="I6" s="91" t="inlineStr">
+        <is>
+          <t>Peak Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K-6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>180</v>
+      </c>
+      <c r="D7" s="93" t="inlineStr">
+        <is>
+          <t>C-PESPreservation Row 87 / I-Withdrawal Row 127; Superintendent estimate</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105</v>
+      </c>
+      <c r="F7" s="96" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>114</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Oct 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DCS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K-6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="93" t="inlineStr">
+        <is>
+          <t>Est. from peak enrollment (473, Oct 2023) + operational margin</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>467</v>
+      </c>
+      <c r="F8" s="96" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" t="n">
+        <v>473</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Oct 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MSS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PreK-2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>330</v>
+      </c>
+      <c r="D9" s="93" t="inlineStr">
+        <is>
+          <t>15 classrooms x 22 students = 330; peak was 327 (Oct 2022)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>274</v>
+      </c>
+      <c r="F9" s="96" t="n">
+        <v>0.8303030303030303</v>
+      </c>
+      <c r="G9" t="n">
+        <v>56</v>
+      </c>
+      <c r="H9" t="n">
+        <v>327</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Oct 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>280</v>
+      </c>
+      <c r="D10" s="93" t="inlineStr">
+        <is>
+          <t>Est. from peak enrollment (286, Oct 2012) + small margin</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>264</v>
+      </c>
+      <c r="F10" s="96" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>286</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Oct 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>350</v>
+      </c>
+      <c r="D11" s="93" t="inlineStr">
+        <is>
+          <t>Est. from peak enrollment (356, Oct 2017) + operational margin</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>306</v>
+      </c>
+      <c r="F11" s="96" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="G11" t="n">
+        <v>44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>356</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Oct 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FHS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9-12</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>650</v>
+      </c>
+      <c r="D12" s="93" t="inlineStr">
+        <is>
+          <t>PDT Architects study (2013): 650 at 80% utilization, 780 at 90%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>554</v>
+      </c>
+      <c r="F12" s="96" t="n">
+        <v>0.8523076923076923</v>
+      </c>
+      <c r="G12" t="n">
+        <v>96</v>
+      </c>
+      <c r="H12" t="n">
+        <v>632</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Oct 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2290</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G13" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t>2. METHODOLOGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PES: 180 from FY28 workbook (C-PESPreservation, I-Withdrawal). Superintendent confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FHS: 650 at 80% from PDT Architects 2013 Concept Design Report (FC-2013-01-09-minutes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DCS, MLS, FMS: Estimated as peak historical enrollment + 5-7% operational margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MSS: 5 kindergarten + 5 first + 5 second grade classrooms = 15 classrooms. At 22 students/class = 330.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Enrollment source: Oct 1 headcounts from Superintendent Handbooks (I-Enrollment, C-SchoolBudgets in Overview).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>All estimates are preliminary. Facilities study results will provide definitive figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Sections 1.6, 1.7, 2.4, 4.5.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: MSS Facilities Risk and Deferred Maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Inventory of identified but unfunded MSS capital projects from Finance Committee capital plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All costs from FC presentations (2015-2022). See data/RSU 5 Finance Committee/md/ for source documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. DEFERRED MAINTENANCE INVENTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>Est. Cost</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="inlineStr">
+        <is>
+          <t>Source Document</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>Year First Identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HVAC: gym/kitchen/office unit replacement</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C7" s="93" t="inlineStr">
+        <is>
+          <t>2021-10-13 Capital Plan: "to be replaced"</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Unfunded</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Elevator upgrade</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>2021-10-13 Capital Plan (prev. $40K-$65K)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Deferred since FY20</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exterior door replacement</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C9" s="93" t="inlineStr">
+        <is>
+          <t>2020-10-28 Capital Plan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Deferred from FY25</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fire alarm upgrade</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>2016-11-30 Capital Plan (5-Year)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deferred since FY22</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Phone system</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C11" s="93" t="inlineStr">
+        <is>
+          <t>2021-10-13 Capital Plan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Planned FY27</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Key card access control (shared w/ PES)</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>2020-10-28 Capital Plan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Planned FY26</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Playground paving</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C13" s="93" t="inlineStr">
+        <is>
+          <t>2021-10-13 Capital Plan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Planned FY27</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="91" t="inlineStr">
+        <is>
+          <t>TOTAL IDENTIFIED DEFERRED MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>420000</v>
+      </c>
+      <c r="C14" s="93" t="inlineStr">
+        <is>
+          <t>Sum of above. Excludes structural/roofing/major HVAC work the facilities study may identify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t>2. MAJOR RENOVATION COST ESTIMATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Based on FHS renovation precedent (PDT Architects, 2013-2016):</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr">
+        <is>
+          <t>Source/Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FHS renovation total (2013)</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="C19" s="93" t="inlineStr">
+        <is>
+          <t>FC-2013-01-09-minutes; PDT Architects Concept Design Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inflation adjustment (2013 to 2026, ~35%)</t>
+        </is>
+      </c>
+      <c r="B20" s="97" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C20" s="93" t="inlineStr">
+        <is>
+          <t>CPI construction cost index estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FHS inflation-adjusted equivalent</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>22882500</v>
+      </c>
+      <c r="C21" s="93" t="inlineStr">
+        <is>
+          <t>16,950,000 x 1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MSS size relative to FHS (est.)</t>
+        </is>
+      </c>
+      <c r="B22" s="97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="93" t="inlineStr">
+        <is>
+          <t>MSS is smaller building (K-2 vs 9-12); fewer specialized spaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MSS renovation low estimate</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C23" s="93" t="inlineStr">
+        <is>
+          <t>Conservative: smaller scope, some systems already updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MSS renovation high estimate</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="C24" s="93" t="inlineStr">
+        <is>
+          <t>If structural/roofing/full HVAC scope identified by facilities study</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>3. CAPITAL RESERVES STATUS (FY27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Source: FY27 Superintendent Handbook, Capital Projects Reserve Account section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B28" s="91" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C28" s="91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Capital Projects Reserve (beginning FY27)</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>2420008</v>
+      </c>
+      <c r="C29" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Less: PES Septic</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>-290474</v>
+      </c>
+      <c r="C30" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Less: Life Safety Cameras &amp; Door Access</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>-483269</v>
+      </c>
+      <c r="C31" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Less: Track/Turf Curbing</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>-27495</v>
+      </c>
+      <c r="C32" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Less: DCS Building Automation</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="C33" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Less: FHS Variable Flow Pump</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="C34" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Less: FHS Tennis Court Design</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>-41500</v>
+      </c>
+      <c r="C35" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Less: Capital Projects (general)</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>-81000</v>
+      </c>
+      <c r="C36" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Less: Facilities Study</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="C37" s="93" t="inlineStr">
+        <is>
+          <t>Board vote Feb 25, 2026 (11-0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PROJECTED ENDING BALANCE</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>1311270</v>
+      </c>
+      <c r="C38" s="93" t="inlineStr">
+        <is>
+          <t>Sum of above</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Sections 1.6, 1.7.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: Impact on RSU 5 if Pownal Withdraws</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models revenue/cost changes for the remaining district (Durham + Freeport).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All inputs from I-Revenue, I-Budget, C-Consumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. REVENUE LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pownal leaves RSU 5. All Pownal revenue (RLC + ALM + State Aid) is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C7" s="91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pownal RLC (lost)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>2257247</v>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pownal ALM (lost)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>2190978</v>
+      </c>
+      <c r="C9" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pownal State Aid (lost)</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>567180</v>
+      </c>
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>I-Revenue Row 11; state aid follows students, not district</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE LOSS</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>5015405</v>
+      </c>
+      <c r="C11" s="93" t="inlineStr">
+        <is>
+          <t>Sum of above</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>2. COST SAVINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PES direct costs eliminated. Secondary savings from fewer students at shared schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Variable cost savings at FMS/FHS are lower than average cost because fixed costs remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B16" s="91" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C16" s="91" t="inlineStr">
+        <is>
+          <t>Source/Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PES direct budget eliminated</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>2270105</v>
+      </c>
+      <c r="C17" s="93" t="inlineStr">
+        <is>
+          <t>I-Budget: sum of PES articles 1+2+4+5+7+9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Less: PES building ops retained (if building kept)</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>-253384</v>
+      </c>
+      <c r="C18" s="93" t="inlineStr">
+        <is>
+          <t>I-Budget: PES Art 9 (facility costs continue if building not sold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Net PES cost savings</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>2016721</v>
+      </c>
+      <c r="C19" s="93" t="inlineStr">
+        <is>
+          <t>2,270,105 - 253,384</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>System-wide pool reduction (Pownal share)</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>543093</v>
+      </c>
+      <c r="C21" s="93" t="inlineStr">
+        <is>
+          <t>C-Consumption: Pownal share of system pool (10.41% x $5.22M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FMS savings (45 Pownal students leave)</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>236250</v>
+      </c>
+      <c r="C22" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity: 45 students x ~$5,250 variable cost per FMS student</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FHS savings (55 Pownal students leave)</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>291500</v>
+      </c>
+      <c r="C23" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity: 55 students x ~$5,300 variable cost per FHS student</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GROSS COST SAVINGS</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>3087564</v>
+      </c>
+      <c r="C25" s="93" t="inlineStr">
+        <is>
+          <t>Sum of positive items above</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>3. TUITION REVENUE OFFSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>If Pownal tuitions 6-12 students back to RSU 5 schools:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B29" s="91" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C29" s="91" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pownal students tuitioning to FMS/FHS</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" s="93" t="inlineStr">
+        <is>
+          <t>I-Equity: 45 FMS + 55 FHS students</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estimated tuition rate per student</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C31" s="93" t="inlineStr">
+        <is>
+          <t>Conservative estimate; actual tuition TBD by negotiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ANNUAL TUITION REVENUE</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C32" s="93" t="inlineStr">
+        <is>
+          <t>100 students x $7,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>4. NET IMPACT ON RSU 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B35" s="91" t="inlineStr">
+        <is>
+          <t>Revenue Loss</t>
+        </is>
+      </c>
+      <c r="C35" s="91" t="inlineStr">
+        <is>
+          <t>Cost Savings</t>
+        </is>
+      </c>
+      <c r="D35" s="91" t="inlineStr">
+        <is>
+          <t>Tuition Revenue</t>
+        </is>
+      </c>
+      <c r="E35" s="91" t="inlineStr">
+        <is>
+          <t>Net Shortfall</t>
+        </is>
+      </c>
+      <c r="F35" s="91" t="inlineStr">
+        <is>
+          <t>% of Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Without tuition</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>5015405</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>3087564</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>1927841</v>
+      </c>
+      <c r="F36" s="98" t="n">
+        <v>0.04070830178514079</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>With tuition revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>5015405</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>3087564</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>750000</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>1177841</v>
+      </c>
+      <c r="F37" s="98" t="n">
+        <v>0.02487129741659817</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>5. PER-HOUSEHOLD IMPACT ON REMAINING TOWNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shortfall absorbed by Durham and Freeport, allocated by remaining ALM shares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="B41" s="91" t="inlineStr">
+        <is>
+          <t>ALM Share (excl Pownal)</t>
+        </is>
+      </c>
+      <c r="C41" s="91" t="inlineStr">
+        <is>
+          <t>Shortfall Share</t>
+        </is>
+      </c>
+      <c r="D41" s="91" t="inlineStr">
+        <is>
+          <t>Households</t>
+        </is>
+      </c>
+      <c r="E41" s="91" t="inlineStr">
+        <is>
+          <t>Per Household/Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Durham</t>
+        </is>
+      </c>
+      <c r="B42" s="98" t="n">
+        <v>0.2450800917313314</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>288665</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="B43" s="98" t="n">
+        <v>0.7549199082686686</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>889176</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Section 6.8, Executive Summary.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: Statewide Benchmarks and Cost Driver Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Per-pupil expenditure data from Maine DOE Resident Expenditure Reports (MEFS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: maine.gov/doe/funding/reports/expenditures. FY23 (pub 1/8/2024), FY24 (pub 1/7/2025), FY25 (pub 1/7/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. RSU 5 vs. STATE AVERAGE (Per-Pupil Expenditure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="D6" s="91" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>2-Year Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RSU 5 per pupil</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>16757</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>18029</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>20344</v>
+      </c>
+      <c r="E7" s="98" t="n">
+        <v>0.2140597959061885</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>State average per pupil</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>17655</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>18316</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>19804</v>
+      </c>
+      <c r="E8" s="98" t="n">
+        <v>0.1217218918153498</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RSU 5 vs. state</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>-898</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>-287</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RSU 5 vs. state (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="98" t="n">
+        <v>-0.0508637779665817</v>
+      </c>
+      <c r="C10" s="98" t="n">
+        <v>-0.01566936012229747</v>
+      </c>
+      <c r="D10" s="98" t="n">
+        <v>0.0272672187436882</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RSU 5 enrollment</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>2069</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2089</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E12" s="98" t="n">
+        <v>-0.03286611889801838</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>State enrollment</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>166797</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>170519</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>168611</v>
+      </c>
+      <c r="E13" s="98" t="n">
+        <v>0.01087549536262644</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RSU 5 total spending (est.)</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>34678</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>37667</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>40709</v>
+      </c>
+      <c r="E15" s="98" t="n">
+        <v>0.1739142972489762</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>State total spending (est., $M)</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>2946</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>3124</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>3339</v>
+      </c>
+      <c r="E16" s="98" t="n">
+        <v>0.1334012219959266</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>2. PEER DISTRICT COMPARISON (Per-Pupil, FY25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Selected RSUs/MSADs in southern/coastal Maine with 1,000-3,000 students.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B20" s="91" t="inlineStr">
+        <is>
+          <t>FY25 Per-Pupil</t>
+        </is>
+      </c>
+      <c r="C20" s="91" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="D20" s="91" t="inlineStr">
+        <is>
+          <t>vs. State Avg</t>
+        </is>
+      </c>
+      <c r="E20" s="91" t="inlineStr">
+        <is>
+          <t>FY23-FY25 Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RSU 75/MSAD 75 (Topsham)</t>
+        </is>
+      </c>
+      <c r="B21" s="99" t="n">
+        <v>24452</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>2287</v>
+      </c>
+      <c r="D21" s="100" t="n">
+        <v>0.2347000605938194</v>
+      </c>
+      <c r="E21" s="98" t="n">
+        <v>0.3132116004296455</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RSU 21 (Kennebunk)</t>
+        </is>
+      </c>
+      <c r="B22" s="99" t="n">
+        <v>23866</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D22" s="100" t="n">
+        <v>0.2051100787719653</v>
+      </c>
+      <c r="E22" s="98" t="n">
+        <v>0.0474894662921348</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RSU 51/MSAD 51 (Cumberland)</t>
+        </is>
+      </c>
+      <c r="B23" s="99" t="n">
+        <v>22054</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>2228</v>
+      </c>
+      <c r="D23" s="100" t="n">
+        <v>0.113613411432034</v>
+      </c>
+      <c r="E23" s="98" t="n">
+        <v>0.1038038038038038</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RSU 05 (Freeport/Durham/Pownal)</t>
+        </is>
+      </c>
+      <c r="B24" s="99" t="n">
+        <v>20344</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D24" s="100" t="n">
+        <v>0.0272672187436882</v>
+      </c>
+      <c r="E24" s="98" t="n">
+        <v>0.2140597959061885</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RSU 10 (Rumford)</t>
+        </is>
+      </c>
+      <c r="B25" s="99" t="n">
+        <v>20271</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>1728</v>
+      </c>
+      <c r="D25" s="100" t="n">
+        <v>0.02358109472833769</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STATE AVERAGE</t>
+        </is>
+      </c>
+      <c r="B26" s="99" t="n">
+        <v>19804</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>168611</v>
+      </c>
+      <c r="D26" s="100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="98" t="n">
+        <v>0.1217218918153498</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RSU 12 (Westbrook)</t>
+        </is>
+      </c>
+      <c r="B27" s="99" t="n">
+        <v>19720</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D27" s="100" t="n">
+        <v>-0.004241567360129261</v>
+      </c>
+      <c r="E27" s="98" t="n">
+        <v>0.2960893854748603</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RSU 02 (Hallowell)</t>
+        </is>
+      </c>
+      <c r="B28" s="99" t="n">
+        <v>19891</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>1419</v>
+      </c>
+      <c r="D28" s="100" t="n">
+        <v>0.004393051908705203</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RSU 14 (Windham)</t>
+        </is>
+      </c>
+      <c r="B29" s="99" t="n">
+        <v>18664</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>3083</v>
+      </c>
+      <c r="D29" s="100" t="n">
+        <v>-0.05756412845889725</v>
+      </c>
+      <c r="E29" s="98" t="n">
+        <v>0.1495442227149544</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RSU 22 (Hampden)</t>
+        </is>
+      </c>
+      <c r="B30" s="99" t="n">
+        <v>17919</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D30" s="100" t="n">
+        <v>-0.09518279135528174</v>
+      </c>
+      <c r="E30" s="98" t="n">
+        <v>0.2830445367320635</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RSU 16 (Poland)</t>
+        </is>
+      </c>
+      <c r="B31" s="99" t="n">
+        <v>16453</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>1661</v>
+      </c>
+      <c r="D31" s="100" t="n">
+        <v>-0.1692082407594425</v>
+      </c>
+      <c r="E31" s="98" t="n">
+        <v>0.1391677629301391</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RSU 34 (Belfast)</t>
+        </is>
+      </c>
+      <c r="B32" s="99" t="n">
+        <v>15921</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>1224</v>
+      </c>
+      <c r="D32" s="100" t="n">
+        <v>-0.1960715007069279</v>
+      </c>
+      <c r="E32" s="98" t="n">
+        <v>0.07465406682416464</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>3. RSU 5 SPENDING BY CATEGORY vs. STATE (FY25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B35" s="91" t="inlineStr">
+        <is>
+          <t>RSU 5</t>
+        </is>
+      </c>
+      <c r="C35" s="91" t="inlineStr">
+        <is>
+          <t>State Avg</t>
+        </is>
+      </c>
+      <c r="D35" s="91" t="inlineStr">
+        <is>
+          <t>RSU 5 vs. State</t>
+        </is>
+      </c>
+      <c r="E35" s="91" t="inlineStr">
+        <is>
+          <t>RSU 5 FY23</t>
+        </is>
+      </c>
+      <c r="F35" s="91" t="inlineStr">
+        <is>
+          <t>RSU 5 2-Yr Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regular Instruction</t>
+        </is>
+      </c>
+      <c r="B36" s="99" t="n">
+        <v>9074</v>
+      </c>
+      <c r="C36" s="99" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D36" s="100" t="n">
+        <v>0.2018543046357615</v>
+      </c>
+      <c r="E36" s="99" t="n">
+        <v>7406</v>
+      </c>
+      <c r="F36" s="98" t="n">
+        <v>0.2252227923305428</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Special Education</t>
+        </is>
+      </c>
+      <c r="B37" s="99" t="n">
+        <v>2863</v>
+      </c>
+      <c r="C37" s="99" t="n">
+        <v>3747</v>
+      </c>
+      <c r="D37" s="100" t="n">
+        <v>-0.2359220709901254</v>
+      </c>
+      <c r="E37" s="99" t="n">
+        <v>2366</v>
+      </c>
+      <c r="F37" s="98" t="n">
+        <v>0.2100591715976332</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Career &amp; Tech Ed</t>
+        </is>
+      </c>
+      <c r="B38" s="99" t="n">
+        <v>145</v>
+      </c>
+      <c r="C38" s="99" t="n">
+        <v>320</v>
+      </c>
+      <c r="D38" s="100" t="n">
+        <v>-0.546875</v>
+      </c>
+      <c r="E38" s="99" t="n">
+        <v>89</v>
+      </c>
+      <c r="F38" s="98" t="n">
+        <v>0.6292134831460674</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Instruction</t>
+        </is>
+      </c>
+      <c r="B39" s="99" t="n">
+        <v>516</v>
+      </c>
+      <c r="C39" s="99" t="n">
+        <v>436</v>
+      </c>
+      <c r="D39" s="100" t="n">
+        <v>0.1834862385321101</v>
+      </c>
+      <c r="E39" s="99" t="n">
+        <v>444</v>
+      </c>
+      <c r="F39" s="98" t="n">
+        <v>0.1621621621621621</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Student &amp; Staff Support</t>
+        </is>
+      </c>
+      <c r="B40" s="99" t="n">
+        <v>2175</v>
+      </c>
+      <c r="C40" s="99" t="n">
+        <v>1657</v>
+      </c>
+      <c r="D40" s="100" t="n">
+        <v>0.3126131563065782</v>
+      </c>
+      <c r="E40" s="99" t="n">
+        <v>1636</v>
+      </c>
+      <c r="F40" s="98" t="n">
+        <v>0.3294621026894866</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>System Administration</t>
+        </is>
+      </c>
+      <c r="B41" s="99" t="n">
+        <v>598</v>
+      </c>
+      <c r="C41" s="99" t="n">
+        <v>696</v>
+      </c>
+      <c r="D41" s="100" t="n">
+        <v>-0.1408045977011494</v>
+      </c>
+      <c r="E41" s="99" t="n">
+        <v>484</v>
+      </c>
+      <c r="F41" s="98" t="n">
+        <v>0.2355371900826446</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>School Administration</t>
+        </is>
+      </c>
+      <c r="B42" s="99" t="n">
+        <v>1146</v>
+      </c>
+      <c r="C42" s="99" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D42" s="100" t="n">
+        <v>0.1312931885488648</v>
+      </c>
+      <c r="E42" s="99" t="n">
+        <v>901</v>
+      </c>
+      <c r="F42" s="98" t="n">
+        <v>0.2719200887902331</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="B43" s="99" t="n">
+        <v>861</v>
+      </c>
+      <c r="C43" s="99" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D43" s="100" t="n">
+        <v>-0.212259835315645</v>
+      </c>
+      <c r="E43" s="99" t="n">
+        <v>717</v>
+      </c>
+      <c r="F43" s="98" t="n">
+        <v>0.2008368200836821</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="B44" s="99" t="n">
+        <v>2319</v>
+      </c>
+      <c r="C44" s="99" t="n">
+        <v>2238</v>
+      </c>
+      <c r="D44" s="100" t="n">
+        <v>0.03619302949061654</v>
+      </c>
+      <c r="E44" s="99" t="n">
+        <v>2142</v>
+      </c>
+      <c r="F44" s="98" t="n">
+        <v>0.08263305322128844</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Debt Service</t>
+        </is>
+      </c>
+      <c r="B45" s="99" t="n">
+        <v>555</v>
+      </c>
+      <c r="C45" s="99" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D45" s="100" t="n">
+        <v>-0.4515810276679841</v>
+      </c>
+      <c r="E45" s="99" t="n">
+        <v>571</v>
+      </c>
+      <c r="F45" s="98" t="n">
+        <v>-0.02802101576182137</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>All Other</t>
+        </is>
+      </c>
+      <c r="B46" s="99" t="n">
+        <v>93</v>
+      </c>
+      <c r="C46" s="99" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" s="100" t="n">
+        <v>1.113636363636364</v>
+      </c>
+      <c r="E46" s="99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B47" s="99" t="n">
+        <v>20344</v>
+      </c>
+      <c r="C47" s="99" t="n">
+        <v>19804</v>
+      </c>
+      <c r="D47" s="100" t="n">
+        <v>0.0272672187436882</v>
+      </c>
+      <c r="E47" s="99" t="n">
+        <v>16757</v>
+      </c>
+      <c r="F47" s="98" t="n">
+        <v>0.2140597959061885</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>4. STATEWIDE COST DRIVERS (2024-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Source: Portland Press Herald, Seacoast Online, Central Maine, Maine Monitor, MEA (2025-2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="91" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10-17% annual increases via Maine Education Benefits Trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="93" t="inlineStr">
+        <is>
+          <t>Cumberland-N.Yarmouth: $3M of $4M increase = health insurance. RSU 21: $843K from 12% increase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="91" t="inlineStr">
+        <is>
+          <t>Personnel (78-80% of budgets)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CBA step increases, competitive hiring, new positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="93" t="inlineStr">
+        <is>
+          <t>Westbrook: $2.5M in additional salary+benefits. Personnel = 78-80% of all district budgets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="91" t="inlineStr">
+        <is>
+          <t>Special Education</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Growing caseloads, out-of-district placements, new mandates</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="93" t="inlineStr">
+        <is>
+          <t>Saco: 18% of students in SpEd. EC/CDS transition adds $364K-$664K net new costs by FY28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="91" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Construction, materials, fuel, food, utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="93" t="inlineStr">
+        <is>
+          <t>CPI-adjusted state disbursement growth: 0.7%/yr above inflation (FY06-FY25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t>Enrollment Decline</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fixed costs spread over fewer students</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="93" t="inlineStr">
+        <is>
+          <t>Maine lost 1,908 students statewide FY23-FY25 (-1.1%). RSU 5 lost 68 (-3.3%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="91" t="inlineStr">
+        <is>
+          <t>EPS Formula Gaps</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2004 formula does not reflect current costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="93" t="inlineStr">
+        <is>
+          <t>LD 2226 (2026) proposes overhaul. 40% of districts see state share decrease. MEPRI delivered Feb 2026 update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="91" t="inlineStr">
+        <is>
+          <t>5. FY26-FY27 BUDGET INCREASES AT PEER DISTRICTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="91" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B65" s="91" t="inlineStr">
+        <is>
+          <t>Proposed Increase</t>
+        </is>
+      </c>
+      <c r="C65" s="91" t="inlineStr">
+        <is>
+          <t>Total Budget</t>
+        </is>
+      </c>
+      <c r="D65" s="91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Westbrook</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>9.88%</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>$58.6M</t>
+        </is>
+      </c>
+      <c r="D66" s="93" t="inlineStr">
+        <is>
+          <t>Press Herald 3/9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cumberland-N.Yarmouth (MSAD 51)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7.63%</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>$57.9M</t>
+        </is>
+      </c>
+      <c r="D67" s="93" t="inlineStr">
+        <is>
+          <t>Press Herald 3/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RSU 21 (Kennebunk)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>$62.5M</t>
+        </is>
+      </c>
+      <c r="D68" s="93" t="inlineStr">
+        <is>
+          <t>Seacoast Online 4/2/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Five-Town CSD (Camden area)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>$19.2M</t>
+        </is>
+      </c>
+      <c r="D69" s="93" t="inlineStr">
+        <is>
+          <t>Midcoast Villager 3/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Saco</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>$4.3M (operating)</t>
+        </is>
+      </c>
+      <c r="D70" s="93" t="inlineStr">
+        <is>
+          <t>Citizen Portal, FY25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5.44%</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D71" s="93" t="inlineStr">
+        <is>
+          <t>City of Auburn FY26 budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gray-New Gloucester (MSAD 15)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4.8% (reduced from 6%)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D72" s="93" t="inlineStr">
+        <is>
+          <t>Central Maine 7/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RSU 5 (FY27 proposed)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6.53%</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>$47.4M</t>
+        </is>
+      </c>
+      <c r="D73" s="93" t="inlineStr">
+        <is>
+          <t>FY27 Superintendent Handbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="91" t="inlineStr">
+        <is>
+          <t>6. KEY FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>RSU 5 is NOT a spending outlier. At $20,344/pupil (FY25), it is 2.7% above the state average ($19,804).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>RSU 5 was 5.1% BELOW the state average just two years earlier (FY23). Recent growth is faster than average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nearby comparable districts spend significantly more: RSU 21 ($23,866, +20.5%), RSU 75 ($24,452, +23.5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>RSU 5 spends 20% more than state avg on Regular Instruction (small-school effect) but 24% less on SpEd,</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  21% less on Transportation, and 45% less on Debt Service. Net effect: only 2.7% above average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Budget growth of 5-10%/year is the norm across Maine in 2025-2026, driven by health insurance and CBA costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>The EPS formula (unchanged since 2004) is being overhauled statewide via LD 2226 (2026 legislative session).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>RSU 5 FY27 proposed increase of 6.53% is within the range of peer districts (3.9% to 9.88%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Part III (new Section 3.7), Executive Summary, FAQ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>CALC: Educational Quality and Facility Suitability Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="93" t="inlineStr">
+        <is>
+          <t>Sources: US News &amp; World Report school profiles (2024-25), GreatSchools.org ratings (2024-25),</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="93" t="inlineStr">
+        <is>
+          <t>NeighborhoodScout (Maine DOE assessment data, 2023-24), Maine Chapter 124, Maine DOE Construction Standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>1. STATE ASSESSMENT PROFICIENCY (2023-24 school year, Maine Through Year Assessment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="93" t="inlineStr">
+        <is>
+          <t>Multiple public aggregators report proficiency rates sourced from Maine DOE. Rates below use the most</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="93" t="inlineStr">
+        <is>
+          <t>recent available data. Small sample sizes at PES (~13-15 tested students/grade) increase volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>Grades Tested</t>
+        </is>
+      </c>
+      <c r="C9" s="91" t="inlineStr">
+        <is>
+          <t>Reading Prof.</t>
+        </is>
+      </c>
+      <c r="D9" s="91" t="inlineStr">
+        <is>
+          <t>Math Prof.</t>
+        </is>
+      </c>
+      <c r="E9" s="91" t="inlineStr">
+        <is>
+          <t>GreatSchools Rating</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>US News State Rank</t>
+        </is>
+      </c>
+      <c r="G9" s="91" t="inlineStr">
+        <is>
+          <t>Student-Teacher Ratio</t>
+        </is>
+      </c>
+      <c r="H9" s="91" t="inlineStr">
+        <is>
+          <t>Tested Students/Grade (approx)</t>
+        </is>
+      </c>
+      <c r="I9" s="91" t="inlineStr">
+        <is>
+          <t>Source Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PES (Pownal Elementary)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>85-95%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>75-82%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#10 Elementary</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>9:1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>~13-15</t>
+        </is>
+      </c>
+      <c r="I10" s="93" t="inlineStr">
+        <is>
+          <t>Range reflects NeighborhoodScout (85/82) vs US News (95/75). Small N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DCS (Durham Community)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3-8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>67-93%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#56 Elem / #17 MS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11:1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>~55-65</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="inlineStr">
+        <is>
+          <t>US News: 92/67 (elem+MS combined). Elem math likely higher; MS lowers avg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MLS (Mast Landing)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>73-92%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#36 Elementary</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>11:1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>~80-85</t>
+        </is>
+      </c>
+      <c r="I12" s="93" t="inlineStr">
+        <is>
+          <t>US News: 91/73. NeighborhoodScout: 91/92. Range reflects source differences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MSS (Morse Street)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PK-2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Not rated</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>12:1 (est.)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="inlineStr">
+        <is>
+          <t>No state testing in PK-2. GreatSchools cannot rate without test data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FMS (Freeport Middle)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#11 Middle School</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>~95-100</t>
+        </is>
+      </c>
+      <c r="I14" s="93" t="inlineStr">
+        <is>
+          <t>Reading exceptionally strong. Math below reading but above state avg (49%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FHS (Freeport High)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11 (SAT)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>76-94%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>56-95%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#18 High School</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>13:1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>~140-150</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="inlineStr">
+        <is>
+          <t>SAT-based. Graduation 95%+. SAT avg 1220. AP pass rate 77%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="93" t="inlineStr">
+        <is>
+          <t>Maine state averages (2023-24): Elementary Reading ~61%, Math ~57%. Middle Reading ~84%, Math ~49%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="93" t="inlineStr">
+        <is>
+          <t>RSU 5 district rank: #16 of 189 Maine school districts (top 10%). Source: Public School Review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>2. SAMPLE SIZE AND STATISTICAL RELIABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B21" s="91" t="inlineStr">
+        <is>
+          <t>Approx Students Tested/Grade</t>
+        </is>
+      </c>
+      <c r="C21" s="91" t="inlineStr">
+        <is>
+          <t>Single Student Impact on Proficiency Rate</t>
+        </is>
+      </c>
+      <c r="D21" s="91" t="inlineStr">
+        <is>
+          <t>Implication</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>~13-15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6.7% to 7.7%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Year-to-year swings of 10-15 points are expected from normal variation alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DCS (elem grades)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>~55-65</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.5% to 1.8%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stable estimates. Multi-year trends are meaningful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>~80-85</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.2% to 1.3%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Most stable elementary estimates in the district.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>~95-100</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.0% to 1.1%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stable. Trends are meaningful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="93" t="inlineStr">
+        <is>
+          <t>Calculation: 1 / (students tested per grade). PES: 1/15 = 6.7%. DCS: 1/60 = 1.7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>3. FACILITY SUITABILITY FOR EDUCATIONAL PROGRAMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B30" s="91" t="inlineStr">
+        <is>
+          <t>PES (Pownal)</t>
+        </is>
+      </c>
+      <c r="C30" s="91" t="inlineStr">
+        <is>
+          <t>DCS (Durham)</t>
+        </is>
+      </c>
+      <c r="D30" s="91" t="inlineStr">
+        <is>
+          <t>MSS (Freeport)</t>
+        </is>
+      </c>
+      <c r="E30" s="91" t="inlineStr">
+        <is>
+          <t>MLS (Freeport)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rural, Elmwood Road</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rural/suburban, Hallowell Rd</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Downtown urban, Morse St</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Suburban, Mollymauk Lane</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Site size</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ample (rural parcel)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>~15+ acres (purpose-built 2010)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Constrained urban lot</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Moderate suburban</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Older, well-maintained</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>87,521 sq ft (built 2010, $15.66M)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Multi-wing, aging</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Renovated 2017-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Outdoor play areas</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Playground + open fields + natural areas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3 play fields, baseball, softball, soccer, basketball, garden</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1 playground ONLY (no fields)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Playground + limited fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Natural environment</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Access to Runaround Pond, wooded areas</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Adjacent fields and nature areas</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>None (downtown commercial area)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Some wooded areas nearby</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Room to expand</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yes (rural lot)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Limited (built to capacity)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No (surrounded by residential/commercial)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Playground condition</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Basketball court resurfacing planned</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Modern (2010 construction)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Equipment replaced 2018; paving deferred since 2019 ($25K unfunded)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Maintained</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Safety concerns</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>None documented</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>None documented</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Stray baseballs from FHS fields required $22K safety netting (2016)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>None documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PreK outdoor compliance</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>75 sq ft/child met (ample space)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A (no PreK program)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>75 sq ft/child: 64 PreK students = 4,800 sq ft required. Constrained.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>N/A (grades 3-5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EC suitability (Ch. 124)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Strong: rural space, natural light, room</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Weak: constrained outdoor space, proximity to traffic, limited expansion</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="91" t="inlineStr">
+        <is>
+          <t>4. MAINE CHAPTER 124 OUTDOOR REQUIREMENTS (Preschool Programs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="93" t="inlineStr">
+        <is>
+          <t>Source: 05 CMR 071-124-9 (Maine Rules for Public Preschool Programs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="B44" s="91" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C44" s="91" t="inlineStr">
+        <is>
+          <t>MSS Status</t>
+        </is>
+      </c>
+      <c r="D44" s="91" t="inlineStr">
+        <is>
+          <t>PES Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Indoor space per child</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>35 sq ft minimum</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Met (existing PreK rooms 130, 131)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Outdoor space per child</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>75 sq ft usable space</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Constrained: 64 PreK = 4,800 sq ft required</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Met: ample rural outdoor space</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Fencing/barriers</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fenced or naturally barriered</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fencing installed 2023</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Natural barriers + fencing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Equipment sizing</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sized for 4-year-olds per NSPS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Equipment replaced 2018</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Equipment available</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Surface under equipment</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Energy-absorbing (no concrete/asphalt)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Playground paving deferred since 2019</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Shade and sun</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Both required</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Limited (urban lot, minimal trees)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Met (rural setting, natural shade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ADA accessibility</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Elevator aging, deferred since 2016</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Single-story, accessible</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Water source in classroom</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Natural light</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="91" t="inlineStr">
+        <is>
+          <t>5. MAINE DOE CONSTRUCTION STANDARDS (New/Renovated Schools)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="93" t="inlineStr">
+        <is>
+          <t>Source: Maine DOE Standards &amp; Guidelines for New School Construction (May 2015, rev. Oct 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="93" t="inlineStr">
+        <is>
+          <t>If MSS undergoes major renovation requiring state funding, it must meet these standards:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t>Requirement (PreK-3)</t>
+        </is>
+      </c>
+      <c r="B59" s="91" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C59" s="91" t="inlineStr">
+        <is>
+          <t>MSS Feasibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hard play area</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Required, proportional to enrollment</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Existing playground; paving deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Soft play area</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Required, proportional to enrollment</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Limited; no dedicated soft play area</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>All-purpose field</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Required, proportional to enrollment</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NO field space on site</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Playground equipment budget</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>$160/student</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>274 students x $160 = $43,840</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Play areas away from vehicles</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Constrained: parking lot adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chain link perimeter fencing</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Installed 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="91" t="inlineStr">
+        <is>
+          <t>6. RESEARCH: SCHOOL CONSOLIDATION AND STUDENT OUTCOMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="91" t="inlineStr">
+        <is>
+          <t>Krueger (1999), Project STAR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tennessee class size experiment</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="93" t="inlineStr">
+        <is>
+          <t>Small classes (13-17) produced 4 percentile point gain. Effects strongest in early grades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="91" t="inlineStr">
+        <is>
+          <t>Chetty et al. (2011)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Long-term STAR follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="93" t="inlineStr">
+        <is>
+          <t>Small class benefits persist to adulthood: higher college attendance, higher earnings, even after test score fadeout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="91" t="inlineStr">
+        <is>
+          <t>Heinesen (2022, IZA)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Danish school consolidation study</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="93" t="inlineStr">
+        <is>
+          <t>Short-term negative effects on achievement, most pronounced for students from small schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="91" t="inlineStr">
+        <is>
+          <t>Coulson &amp; Bhatt (2022, EdPolicy)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Arkansas consolidation study</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="93" t="inlineStr">
+        <is>
+          <t>Null or small positive effects. No evidence of classroom-level economies of scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="91" t="inlineStr">
+        <is>
+          <t>Cooley &amp; Floyd (2013, ERIC)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Texas small rural consolidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="93" t="inlineStr">
+        <is>
+          <t>Per-pupil costs INCREASED while achievement DECREASED for absorbing districts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="91" t="inlineStr">
+        <is>
+          <t>Campbell Collaboration (2021)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Systematic review of class size research</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="93" t="inlineStr">
+        <is>
+          <t>Small-to-zero average effect outside STAR, but context-dependent. Benefits most for disadvantaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="91" t="inlineStr">
+        <is>
+          <t>7. KEY FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>All RSU 5 schools with tested grades substantially outperform Maine state averages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PES achieves GreatSchools 8/10 and is ranked in the top 10 Maine elementary schools (US News).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PES has the best student-teacher ratio in the district (9:1 vs 10:1 to 13:1 at other schools).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PES proficiency data must be interpreted with caution due to small sample sizes (~13-15 per grade).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>The research literature does NOT support improved educational outcomes from consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Project STAR and Chetty (2011) demonstrate lasting benefits of small classes, particularly in early grades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MSS is the least suitable RSU 5 school for early childhood programs: no fields, constrained outdoor space,</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  documented safety issues, and difficulty meeting Ch. 124 and DOE construction standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PES is the most suitable site for EC programs: ample outdoor space, natural environment, Ch. 124 compliant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Closing PES (Path B) would move 105 students from 9:1 to 11:1 student-teacher ratio at DCS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DCS (purpose-built 2010, 87,521 sq ft) is designed for larger populations but is already at ~93% utilization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="93" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Section 1.8, Section 4.6, Executive Summary, FAQ.</t>
         </is>
       </c>
     </row>
@@ -16917,7 +22361,7 @@
       <c r="B20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="78" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -16930,7 +22374,7 @@
       <c r="B21" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16943,7 +22387,7 @@
       <c r="B22" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16956,7 +22400,7 @@
       <c r="B23" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16969,7 +22413,7 @@
       <c r="B24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16982,7 +22426,7 @@
       <c r="B25" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16995,7 +22439,7 @@
       <c r="B26" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17863,7 +23307,7 @@
           <t>Total Mil Rate</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="79" t="n">
         <v>15.3</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -17878,7 +23322,7 @@
           <t>RSU Share of Tax</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="80" t="n">
         <v>0.584</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -17893,7 +23337,7 @@
           <t>County Share of Tax</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="80" t="n">
         <v>0.033</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -17908,7 +23352,7 @@
           <t>Town Share of Tax</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="80" t="n">
         <v>0.383</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -18005,7 +23449,7 @@
           <t>Total Mil Rate</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="79" t="n">
         <v>13.85</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -18020,7 +23464,7 @@
           <t>RSU Share (FY25 proxy)</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="80" t="n">
         <v>0.716</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -18117,7 +23561,7 @@
           <t>Total Mil Rate</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="79" t="n">
         <v>33.58</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -18839,7 +24283,7 @@
           <t>PES full conversion multiplier</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="78" t="n">
         <v>1.75</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -18884,7 +24328,7 @@
           <t>Support services efficiency (PES closure)</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="80" t="n">
         <v>0.5</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -18974,7 +24418,7 @@
           <t>Birth rate per 1,000 [Fn 14]</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="78" t="n">
         <v>9.5</v>
       </c>
       <c r="C27" s="4" t="inlineStr">

--- a/FY28/RSU5_FY28_Projection.xlsx
+++ b/FY28/RSU5_FY28_Projection.xlsx
@@ -744,8 +744,9 @@
           <t>PES cost per student (from analysis)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>24247</v>
+      <c r="B10" s="5">
+        <f>'C-CostPremium'!B12</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -754,8 +755,9 @@
           <t>District avg cost per student</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>15600</v>
+      <c r="B11" s="5">
+        <f>'C-CostPremium'!F12</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -764,8 +766,9 @@
           <t>PES cost premium (fixed-cost dilution)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>8647</v>
+      <c r="B12" s="7">
+        <f>'C-CostPremium'!G12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -819,11 +822,13 @@
           <t>MS consolidation (7-8 at FMS)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>154000</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>154000</v>
+      <c r="B20" s="7">
+        <f>'C-MSConsol'!B21</f>
+        <v/>
+      </c>
+      <c r="C20" s="7">
+        <f>'C-MSConsol'!B21</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -832,11 +837,13 @@
           <t>Additional efficiencies (shared services, scheduling)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>325000</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>650000</v>
+      <c r="B21" s="10">
+        <f>'I-Assumptions'!B22</f>
+        <v/>
+      </c>
+      <c r="C21" s="10">
+        <f>'I-Assumptions'!B23</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -895,77 +902,72 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>PES staff savings (positions eliminated)</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>538500</v>
+          <t>True efficiency savings (marginal teacher + admin + support - coord.)</t>
+        </is>
+      </c>
+      <c r="B29" s="7">
+        <f>'C-FY28Paths'!B33</f>
+        <v/>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>~5 FTE net reduction</t>
+          <t>C-FY28Paths: 2.05 FTE teacher + Art 7 admin + 50% Art 5 - DCS coord.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Additional bus routes (Pownal -&gt; DCS)</t>
-        </is>
-      </c>
-      <c r="B30" s="73" t="n">
-        <v>-225000</v>
+          <t>All transport costs (Pownal-&gt;DCS, Freeport PreK-&gt;PES, Durham PreK-&gt;PES)</t>
+        </is>
+      </c>
+      <c r="B30" s="73">
+        <f>'C-FY28Paths'!B34</f>
+        <v/>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>3 routes @ $75,000/ea</t>
+          <t>C-FY28Paths: 3+3+2 = 8 routes at I-Assumptions cost/route</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>PES building conversion (PreK center)</t>
-        </is>
-      </c>
-      <c r="B31" s="73" t="n">
-        <v>-74375</v>
+          <t>PES EC conversion (amortized per I-Assumptions)</t>
+        </is>
+      </c>
+      <c r="B31" s="73">
+        <f>'C-FY28Paths'!B35</f>
+        <v/>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>$743,750 over 10 yrs</t>
+          <t>C-FY28Paths: I-Assumptions partial x multiplier / years</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>DCS capacity/coordination costs</t>
+          <t>(DCS coordination already included in true efficiency above)</t>
         </is>
       </c>
       <c r="B32" s="73" t="n">
-        <v>-75000</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Additional admin, space prep</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>EC program opt-out risk (families choosing private)</t>
+          <t>(EC opt-out risk modeled in C-RiskModel, not direct cost)</t>
         </is>
       </c>
       <c r="B33" s="73" t="n">
-        <v>-50000</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Transport barrier reduces enrollment</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -981,7 +983,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Path B net: approximately -$161K/year COST (not savings).</t>
+          <t>Path B true net: cost of ~$161K/year (from C-FY28Paths true efficiency lens).</t>
         </is>
       </c>
     </row>
@@ -1155,8 +1157,9 @@
           <t>CDS EC transfer revenue</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n">
-        <v>300000</v>
+      <c r="B51" s="7">
+        <f>AVERAGE('I-ECCosts'!B29,'I-ECCosts'!C29)</f>
+        <v/>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1170,8 +1173,9 @@
           <t>IDEA Part B federal SpEd funding</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
-        <v>125000</v>
+      <c r="B52" s="7">
+        <f>AVERAGE('I-ECCosts'!B30,'I-ECCosts'!C30)</f>
+        <v/>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -1185,8 +1189,9 @@
           <t>EPS PreK state allocation</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>75000</v>
+      <c r="B53" s="7">
+        <f>AVERAGE('I-ECCosts'!B31,'I-ECCosts'!C31)</f>
+        <v/>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -1305,11 +1310,12 @@
         <v>80</v>
       </c>
       <c r="B65" s="16">
-        <f>B29*2/80</f>
-        <v/>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>12361</v>
+        <f>'C-Budget'!D7/A65</f>
+        <v/>
+      </c>
+      <c r="C65" s="7">
+        <f>B65-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D65" s="16">
         <f>B22/80</f>
@@ -1321,11 +1327,12 @@
         <v>90</v>
       </c>
       <c r="B66" s="16">
-        <f>B29*2/90</f>
-        <v/>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>10875</v>
+        <f>'C-Budget'!D7/A66</f>
+        <v/>
+      </c>
+      <c r="C66" s="7">
+        <f>B66-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D66" s="16">
         <f>B22/90</f>
@@ -1337,11 +1344,12 @@
         <v>100</v>
       </c>
       <c r="B67" s="16">
-        <f>B29*2/100</f>
-        <v/>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>9389</v>
+        <f>'C-Budget'!D7/A67</f>
+        <v/>
+      </c>
+      <c r="C67" s="7">
+        <f>B67-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D67" s="16">
         <f>B22/100</f>
@@ -1353,11 +1361,12 @@
         <v>105</v>
       </c>
       <c r="B68" s="16">
-        <f>B29*2/105</f>
-        <v/>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>8647</v>
+        <f>'C-Budget'!D7/A68</f>
+        <v/>
+      </c>
+      <c r="C68" s="7">
+        <f>B68-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D68" s="16">
         <f>B22/105</f>
@@ -1369,11 +1378,12 @@
         <v>110</v>
       </c>
       <c r="B69" s="16">
-        <f>B29*2/110</f>
-        <v/>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>7904</v>
+        <f>'C-Budget'!D7/A69</f>
+        <v/>
+      </c>
+      <c r="C69" s="7">
+        <f>B69-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D69" s="16">
         <f>B22/110</f>
@@ -1385,11 +1395,12 @@
         <v>120</v>
       </c>
       <c r="B70" s="16">
-        <f>B29*2/120</f>
-        <v/>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>6418</v>
+        <f>'C-Budget'!D7/A70</f>
+        <v/>
+      </c>
+      <c r="C70" s="7">
+        <f>B70-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D70" s="16">
         <f>B22/120</f>
@@ -1401,11 +1412,12 @@
         <v>130</v>
       </c>
       <c r="B71" s="16">
-        <f>B29*2/130</f>
-        <v/>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>4932</v>
+        <f>'C-Budget'!D7/A71</f>
+        <v/>
+      </c>
+      <c r="C71" s="7">
+        <f>B71-'C-CostPremium'!F12</f>
+        <v/>
       </c>
       <c r="D71" s="16">
         <f>B22/130</f>
@@ -10847,22 +10859,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Pownal state aid (FY25-26)</t>
+          <t>Pownal total state aid (FY27)</t>
         </is>
       </c>
       <c r="B28" s="7">
-        <f>'I-Tax'!E41</f>
+        <f>'I-Revenue'!B11</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>State aid per PES student</t>
+          <t>State aid per Pownal student (all grades)</t>
         </is>
       </c>
       <c r="B29" s="7">
-        <f>B28/B27</f>
+        <f>B28/'I-Equity'!B24</f>
         <v/>
       </c>
     </row>
@@ -10952,7 +10964,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>At 10% attrition: 10-11 students leave, ~$50K/yr in state revenue lost to RSU 5.</t>
+          <t>At 10% attrition: ~11 students leave, ~$30K/yr in state revenue lost to RSU 5.</t>
         </is>
       </c>
     </row>
@@ -11407,19 +11419,19 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>One-time costs (amortized 5 years)</t>
+          <t>One-time costs (amortized per I-Assumptions)</t>
         </is>
       </c>
       <c r="B75" s="7">
-        <f>B63/5</f>
+        <f>B63/'I-Assumptions'!B19</f>
         <v/>
       </c>
       <c r="C75" s="7">
-        <f>AVERAGE(B63,C63)/5</f>
+        <f>AVERAGE(B63,C63)/'I-Assumptions'!B19</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>C63/5</f>
+        <f>C63/'I-Assumptions'!B19</f>
         <v/>
       </c>
     </row>

--- a/FY28/RSU5_FY28_Projection.xlsx
+++ b/FY28/RSU5_FY28_Projection.xlsx
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-RSUImpact" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-StateBenchmarks" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-EducationQuality" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-ECFacility" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9037,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9064,7 +9065,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FY28 is when EC mandate and any restructuring take effect (2027-2028 school year).</t>
+          <t>EC SpEd Cohort 3 Year 1 (4yo only) begins Fall 2026 (FY27). FY28 adds 3-year-olds and is when structural changes take effect.</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9162,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Step 3: EC Mandate (FY28 new cost)</t>
+          <t>Step 3: EC Mandate (FY28 incremental cost above FY27 lean implementation)</t>
         </is>
       </c>
     </row>
@@ -9176,6 +9177,13 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Range: near-$0 (state funding continues) to Task Force midpoint (if program scales and subsidy ends).</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -9373,6 +9381,48 @@
       <c r="B39" s="22">
         <f>(B37-B7)/B7</f>
         <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PHASED EC COST NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FY27 already includes Cohort 3 Year 1 (4yo only, ~$17,300 net local).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>The EC cost in Step 3 uses the Task Force midpoint as a PLANNING UPPER BOUND for FY28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Actual FY28 EC cost depends on: (1) pace of 3yo expansion, (2) state funding durability, (3) staffing model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>If state incentive funding persists, FY28 EC increment could be well below the Task Force model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>The FY28 baseline range in the omnibus ($50.2M-$50.8M) reflects this uncertainty.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9987,7 +10037,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EC mandate costs and structural changes are NOT in FY27. They are FY28 decisions.</t>
+          <t>NOTE: Initial EC SpEd (Cohort 3 Year 1, 4yo only, ~$17,300 net local) IS in FY27. Structural changes are FY28.</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10504,7 +10554,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NOTE: EC costs are FY28 expenses (begin July 2027), not FY27.</t>
+          <t>NOTE: This models the Task Force Option 1 (comprehensive program). Actual costs depend on phased rollout:</t>
         </is>
       </c>
     </row>
@@ -10587,6 +10637,55 @@
       <c r="D12" s="24">
         <f>B6-B9</f>
         <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PHASED ROLLOUT CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cohort 3 Year 1 (FY27, 2026-2027): 4-year-olds only. Board-approved net local cost: $17,300/yr [Fn 72].</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cohort 3 Year 2 (FY28, 2027-2028): Must add 3-year-olds. Cost uncertain — depends on scope expansion and state funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Full mandate (by July 1, 2028): All children ages 3-5 with disabilities. Task Force model above is upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>State incentive funding covers most Year 1 costs but may decrease as transition period ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>The FY28 EC SpEd increment is the ADDITIONAL cost above the FY27 lean implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Range: near-$0 (state funding continues) to $364K-$664K (full Task Force model, no state subsidy).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -15648,7 +15747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Path A and Path B are FY28 (2027-2028) decisions, not FY27.</t>
+          <t>Path A and Path B are FY28 structural decisions. EC SpEd Cohort 3 Year 1 (4yo) begins FY27; Year 2 (add 3yo) is FY28.</t>
         </is>
       </c>
     </row>
@@ -22088,6 +22187,546 @@
       <c r="A95" s="93" t="inlineStr">
         <is>
           <t>Referenced in: Omnibus Section 1.8, Section 4.6, Executive Summary, FAQ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CALC: EC SpEd Mandate — Facility Modification Cost Estimates by Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Derives facility modification costs required to implement EC SpEd services (LD 345, Cohort 3) under each path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>These are FACILITY costs only. EC SpEd operating costs (staff, contractors, equipment) are in I-ECCosts / C-ECAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>and arrive under ALL paths regardless. This sheet estimates the incremental facility work each path requires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NOTE: "EC SpEd" = the LD 345 mandate (FAPE for ages 3-5 with disabilities). "Community PreK" = existing voluntary preschool programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1. PATH A: Add EC SpEd classroom at MSS (co-located with existing 64-student community PreK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MSS already operates community PreK in rooms 130-131. Adding one EC SpEd classroom is incremental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>References: C-EducationQuality rows 44-53 (Ch. 124 status), C-FacilitiesRisk (deferred items), I-Assumptions A17 (PES conversion as scaling ref).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Low Estimate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>High Estimate</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Source / Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classroom preparation (paint, fixtures, child-height furnishings)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Existing classroom repurposed. Cost per PES partial conversion (25K / ~5 rooms = 5K/room, reduced because MSS already has PreK infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bathroom/plumbing (Ch. 124: toilets within 40 ft, water source in room)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Low: room near existing PreK bathrooms. High: requires new plumbing run. Ch. 124 Section 9 [Fn 21].</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Outdoor space improvements (Ch. 124: 75 sq ft/child, energy-absorbing surface)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Low: existing outdoor area shared with community PreK. High: playground paving (5K, deferred since 2019 per C-FacilitiesRisk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADA compliance — elevator (deferred since 2016 per C-FacilitiesRisk)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Low: EC SpEd classroom on accessible floor. High: elevator upgrade required (0K from C-FacilitiesRisk A8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TOTAL PATH A — MSS EC SpEd Classroom (one-time)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>SUM(B13:B16)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Amortization period (years)</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>I-Assumptions!B19</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>I-Assumptions!B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PATH A — MSS EC SpEd annual amortized cost</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>B17/B18</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>C17/C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PATH A — Midpoint annual amortized cost</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>(B19+C19)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2. PATH B: Convert PES to centralized preschool center (ALL community PreK + EC SpEd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Converts entire K-5 building for district-wide preschool use. All three towns community PreK moves to PES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>References: I-Assumptions A17-A19 (PES conversion cost, multiplier, amortization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PES partial conversion cost</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>I-Assumptions!B17</f>
+        <v/>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>I-Assumptions A17: bathrooms, playground, plumbing [Fn 21][Fn 24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full conversion multiplier</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>I-Assumptions!B18</f>
+        <v/>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>I-Assumptions A18: most rooms need conversion for preschool use</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PES full conversion cost (one-time)</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>B27*B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amortization period (years)</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>I-Assumptions!B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PATH B — PES conversion annual amortized cost</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>B29/B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3. COMPARISON: Annual amortized EC SpEd facility cost by path</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Midpoint</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Path A (MSS: 1 classroom added to existing PreK)</t>
+        </is>
+      </c>
+      <c r="B36">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D36">
+        <f>B20</f>
+        <v/>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Incremental: one room in a school already running 64-student community PreK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Path B (PES: full building conversion to centralized preschool center)</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>B31</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>B31</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>B31</f>
+        <v/>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Full conversion: entire K-5 building becomes preschool center for all three towns</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Difference (Path B minus Path A midpoint)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <f>D37-D36</f>
+        <v/>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Additional annual facility cost of centralizing all PreK at PES vs. adding one EC SpEd classroom at MSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4. KEY ASSUMPTIONS AND LIMITATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>- The elevator (0K) and playground paving (5K) are existing deferred maintenance items (C-FacilitiesRisk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Under Path A, these shift from discretionary to mandatory once EC SpEd students arrive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Under Path B, MSS loses its PreK program entirely, so these items remain discretionary for MSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>- Path A low assumes the selected classroom is near existing PreK infrastructure and on an accessible floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>- Path A high assumes the classroom requires new plumbing and the elevator must be upgraded for ADA/SpEd access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>- Path B cost does not include any savings from avoiding MSS deferred maintenance triggered by keeping PreK at MSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>- Both paths use the same amortization period (I-Assumptions A19) for consistency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>- The facilities study (delivery targeted December 2026 per draft RFQ) will provide professional cost estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  for both MSS and PES modifications. These analyst estimates should be treated as order-of-magnitude projections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Referenced in: Omnibus Sections 2.2 (Path A), 2.3 (Path B), 4.4 (one-time costs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5. MANDATE SCOPE CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Title 20-A sec. 7209-A mandates only EC SpEd (FAPE under Part B, sec. 619). Community PreK is voluntary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Path A requires only an EC SpEd classroom (matches mandate scope).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Path B converts an entire building for all PreK — far exceeds mandate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Board approved Cohort 3 at $17,300/yr net local cost [Fn 72].</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>The facility costs in this sheet are incremental to operating costs in I-ECCosts / C-ECAnalysis.</t>
         </is>
       </c>
     </row>
@@ -23745,7 +24384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -23793,14 +24432,14 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>RSU 5 committed to Cohort 3 (July 2027) per Superintendent's 02/11/2026 presentation [Fn 10].</t>
+          <t>RSU 5 joined Cohort 3 (2026-2027 school year) per Board vote 02/04/2026 [Fn 72]. Superintendent referenced July 2027 in 02/11/2026 presentation [Fn 10].</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>NOTE: EC costs are FY28 expenses (begin July 2027). They do NOT appear in the FY27 budget.</t>
+          <t>NOTE: Cohort 3 services begin Fall 2026 (2026-2027 school year). Full-year cost impact applies to FY28 (begins July 2027).</t>
         </is>
       </c>
     </row>
@@ -24060,6 +24699,204 @@
       </c>
       <c r="C31" s="5" t="n">
         <v>100000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BOARD-APPROVED IMPLEMENTATION (February 4, 2026 — Cohort 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The board approved a leaner implementation than the Task Force modeled above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Most costs are covered by 100% state incentive funding for early-joining districts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Source: Board meeting Feb 4, 2026; Citizen Portal summary [Fn 72].</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Allocation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Funding Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ECSE Coordinator</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0.2 FTE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EC SpEd fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Speech-Language Pathologist</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.9 FTE (reallocated from existing budget)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Existing budget — not new cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SpEd Teacher (282B)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1.0 FTE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>State-funded through EC SpEd program</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EdTechs</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.0 FTE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fully state-funded</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Reported net local impact</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Projected initial enrollment</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>~25 four-year-old students</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RECONCILIATION NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>The Task Force model above reflects a comprehensive school-based program (full coordinator, social worker, contractors).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>The board-approved implementation is much leaner, with most costs covered by 100% state incentive funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Whether the state incentive funding continues at the same level after the statewide July 2028 deadline is unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The omnibus presents both figures and notes the uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MANDATE SCOPE NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Title 20-A sec. 7209-A mandates ONLY EC SpEd (FAPE for Part B, sec. 619 children ages 3-5 with disabilities).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>General/community PreK programs are VOLUNTARY under Maine law (DOE Pre-K Guidebook, Jan 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Scenario 2 (centralizing ALL PreK at PES) substantially exceeds what the mandate requires.</t>
+        </is>
       </c>
     </row>
   </sheetData>
